--- a/Folder_Data.xlsx
+++ b/Folder_Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\katay\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\Ingevia\INGEVIA-Email-Assistance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A7909B32-3F44-42FA-8010-AAF16DF2DC3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04E8540C-DF5A-455C-82E3-D9792D53A0A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{5C19705A-42F0-46F8-960D-DF73BA04C5E9}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="15370" activeTab="1" xr2:uid="{5C19705A-42F0-46F8-960D-DF73BA04C5E9}"/>
   </bookViews>
   <sheets>
     <sheet name="Export Summary" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="641" uniqueCount="455">
   <si>
     <t>This document was exported from Numbers.  Each table was converted to an Excel worksheet. All other objects on each Numbers sheet were placed on separate worksheets. Please be aware that formula calculations may differ in Excel.</t>
   </si>
@@ -1204,63 +1204,6 @@
     <t>-</t>
   </si>
   <si>
-    <t>El proyecto 26-029 corresponde al cliente ENCARNA BOSCH para el año 2026. El alcance del trabajo abarca tareas de urbanismo e ingeniería, específicamente la redacción, modificación y tramitación del Plan General de Ordenación Urbana (PGOU / MPG) para el edificio comercial Nuevo Centro en Valencia, junto con los planos de levantamiento topográfico y CAD asociados (DWG). Incluye además la elaboración y presupuestación de estudios de tráfico y movilidad para una propuesta de instalaciones deportivas con pistas de pádel en la cubierta de dicho centro comercial. Este contexto detallado garantiza que Gemini clasifique con precisión los correos electrónicos sobre Encarna Bosch, borradores del PGOU, modificaciones urbanísticas, estudios de movilidad/tráfico, planos CAD o la instalación deportiva en la cubierta de Nuevo Centro.</t>
-  </si>
-  <si>
-    <t>El proyecto 26-028 corresponde al cliente DIC con ubicación en Alfinach (Puzol) para el año 2026. El alcance de los trabajos abarca la tramitación administrativa y consulta ante la Generalitat Valenciana (GVA) para la solicitud de copia, certificación del estado de vigencia e informes de la Declaración de Interés Comunitario (DIC), gestionado bajo la representación autorizada de Claudio Partearroyo y Miguel Vera. Este contexto detallado permite a la API de Gemini clasificar con precisión futuros correos relacionados con DIC Alfinach/Puzol, solicitudes de informes de vigencia de DIC, autorizaciones de representación ante la GVA o gestiones promovidas por Claudio Partearroyo.</t>
-  </si>
-  <si>
-    <t>El proyecto 26-027 corresponde al cliente SOCUHER para la ubicación La Torreta en el año 2026. El alcance del proyecto comprende la elaboración, revisión y presentación de presupuestos técnicos y ofertas para la implantación o adecuación de una estación de servicio desatendida (gasolinera automática) en La Torreta, gestionado con la interlocución de José Luis Quesada. Esta descripción detallada optimiza el modelo de Gemini para clasificar futuros correos sobre SOCUHER, La Torreta, presupuestos técnicos de estaciones de servicio desatendidas o comunicaciones asociadas a José Luis Quesada.</t>
-  </si>
-  <si>
-    <t>El proyecto 26-026 corresponde al cliente ZONA LOGÍSTICA para la ubicación La Bisbal en el año 2026. El alcance de los trabajos abarca el desarrollo y revisión del estudio de viabilidad técnica y urbanística para la implantación de un almacén o nave logística en La Bisbal, incluyendo la elaboración y coordinación de planos CAD de implantación (DWG), gestionado con la interlocución de Concepción Salmerón. Esta descripción detallada permite a la API de Gemini clasificar con precisión futuros correos relacionados con Zona Logística La Bisbal, estudios de viabilidad de almacenes, planos CAD de implantación o gestiones vinculadas a Concepción Salmerón.</t>
-  </si>
-  <si>
-    <t>El proyecto 26-025 corresponde al cliente PALMETILLO con ubicación en Alcalá de Guadaíra para el año 2026. El alcance de los trabajos contempla el análisis técnico, catastral y urbanístico de parcelas en el ámbito de Palmetillo, incluyendo la revisión de la normativa del Plan Parcial, parámetros de alturas, alineaciones y rasantes, así como la consulta de datos catastrales, gestionado con la intermediación de David Reyero (Reyqueda). Esta descripción detallada permite a la API de Gemini clasificar con precisión futuros correos relacionados con Palmetillo en Alcalá de Guadaíra, datos catastrales, normativa de Plan Parcial, parámetros urbanísticos de alineaciones y rasantes, o gestiones promovidas por David Reyero.</t>
-  </si>
-  <si>
-    <t>El proyecto 26-024 corresponde al cliente PAI GINERMARK con ubicación en Rotglà (Rotglà i Corberà) para el año 2026. El alcance de los trabajos contempla la gestión urbanística y técnica del Programa de Actuación Integrada (PAI) Ginermark, incluyendo el análisis de levantamientos topográficos, la coordinación de la planta base del ámbito y la elaboración de perfiles longitudinales en formato CAD (DWG), bajo la interlocución técnica de Joan Giner. Esta descripción detallada permite a la API de Gemini clasificar con precisión futuros correos relacionados con PAI Ginermark en Rotglà, proyectos de urbanización, levantamientos topográficos, planos CAD de implantación o comunicaciones con Joan Giner.</t>
-  </si>
-  <si>
-    <t>El proyecto 26-023 corresponde al cliente DAYHE para la ubicación Nuevo Centro en el año 2026. El alcance de los trabajos abarca el desarrollo técnico y la tramitación urbanística de la Modificación Puntual del Plan General (MPG) en la zona de Nuevo Centro, así como la estimación presupuestaria y elaboración del estudio de tráfico y movilidad asociado en Valencia, gestionado a través de las gestiones y comunicaciones coordinadas con Encarna. Esta descripción detallada permite a la API de Gemini clasificar con precisión futuros correos relacionados con DAYHE Nuevo Centro, modificaciones puntuales del Plan General (MPG), estudios de tráfico y movilidad en Valencia o gestiones tramitadas con Encarna.</t>
-  </si>
-  <si>
-    <t>El proyecto 26-022 corresponde al cliente SARRIÓN (Estaciones de Servicio Hermanos Sarrión S.L.) con ubicación en Requena para el año 2026. El alcance de los trabajos abarca las gestiones técnicas, proyectos de ingeniería y arquitectura, licencias e intervenciones urbanísticas asociadas a las instalaciones y actividades de estaciones de servicio de la firma en Requena. Esta descripción detallada permite a la API de Gemini clasificar con precisión futuros correos relacionados con Sarrión en Requena, estaciones de servicio, licencias de actividad o proyectos técnicos vinculados a dicha empresa.</t>
-  </si>
-  <si>
-    <t>Encargo de GABTECO MEDIO AMBIENTE S.L. (empresa de ingeniería y medio ambiente, Torrent, Valencia) para la redacción de un proyecto de reparación de caminos y viales rurales dañados (memoria valorada por DANA) en el término municipal de Quart de Poblet, en colaboración con Tragsa/Tragsatec y el Ayuntamiento de Quart de Poblet. La correspondencia típica incluye peticiones de oferta y formalización del encargo, memorias valoradas y mediciones en Presto, planos de ubicación y trazado de los caminos a reparar (PDF/DWG), plantillas de cajetín y anejos, tarifas oficiales de Tragsa, autorizaciones de la Confederación Hidrográfica del Júcar (CHJ), y planos de vados solicitados al Ayuntamiento. Los correos suelen proceder de GABTECO, de personal de Tragsa/Tragsatec, o del Ayuntamiento de Quart de Poblet. Palabras clave: Quart de Poblet, caminos, viales, RP VIALES, DANA, memoria valorada, CHJ, vados, Tragsa.</t>
-  </si>
-  <si>
-    <t>Encargo de FERROVIAL (división Ferrovial Energía, mantenimiento y servicios energéticos) para un proyecto de estructura/cubierta fotovoltaica sobre un aparcamiento en San Fernando (aparentemente en Maspalomas, Gran Canaria, a juzgar por la sede de Ferrovial Energía en Arucas y las referencias "MASP" en los archivos), tramitado a través del promotor MG Desarrollos. El expediente incluye levantamientos topográficos y planos CAD/DWG del solar y del montaje de la estructura, verificación de interferencias entre elementos existentes (báculos de alumbrado) y los pórticos de la estructura principal, el proyecto firmado en PDF, y fichas técnicas de paneles solares (módulos fotovoltaicos LONGi). Los correos suelen proceder de Ferrovial (dominio @ferrovial.com) y de MG Desarrollos (dominio @desarrollosmg.es), dirigidos al equipo de ingeniería de INGEVIA. Palabras clave: San Fernando, Maspalomas, Ferrovial Energía, MG Desarrollos, fotovoltaica, aparcamiento, topográfico, báculo, pórtico, LONGi.</t>
-  </si>
-  <si>
-    <t>Encargo de FENIX GESTION, S.L. (gasolinera y centro de lavado de coches en Torrent) para gestionar la ampliación y prórroga de la autorización/licencia de distribución de carburantes (DIC) de una estación de servicio situada en Serra, con motivo del cambio de titularidad de la instalación (compraventa de la estación a una nueva sociedad titular, antes bajo otra razón social). El expediente incluye la escritura de compraventa y el CIF de la nueva sociedad titular, la solicitud de prórroga y la autorización para tramitar ante la Consellería y el Ayuntamiento (informe municipal vinculante), y los documentos de autorización firmados. Los correos suelen proceder de FENIX GESTION (fenixgestion@outlook.es), dirigidos al equipo de ingeniería de INGEVIA. Palabras clave: Serra, DIC, prórroga, ampliación, gasolinera, estación de servicio, carburantes, compraventa, Consellería, Ayuntamiento.</t>
-  </si>
-  <si>
-    <t>Encargo relacionado con Voladores de Levante (representada por su administrador, Marcos Real) para la tramitación ante el Servicio Territorial de Carreteras de una actividad situada en San Antonio de Benagéber (proyecto identificado en la documentación como "Valencia Greenfield San Antonio Benageber"). El expediente incluye la Memoria Informativa de Actividad en Terreno, el plano de la actividad y de las parcelas afectadas, y la copia simple de la escritura que acredita el nombramiento del administrador. Los correos suelen proceder de la cuenta de contacto de Voladores de Levante (marcossrealm@gmail.com), dirigidos al equipo de ingeniería de INGEVIA para su registro y tramitación. Palabras clave: San Antonio de Benagéber, Voladores de Levante, Greenfield, Memoria Informativa de Actividad en Terreno, parcelas, Territorial de Carreteras.</t>
-  </si>
-  <si>
-    <t>Consulta de ALCALAS ARIN, S.L.P. (Valencia) sobre la posibilidad de instalar parasoles en una parcela situada en el término de Bigastro, junto a la carretera CV-95, y sobre la interpretación de la zona de protección de la carretera (dominio público, servidumbre y afección, línea límite de edificación) para determinar si la parcela es edificable, a raíz de una notificación de Carreteras que fija dicha zona en 50 m (frente a los 25 m que el cliente había previsto). El expediente incluye los planos presentados por el cliente y el análisis/aclaración de INGEVIA sobre la normativa de carreteras aplicable. Los correos suelen proceder de ALCALAS ARIN, S.L.P. (dominio @alcalas.es), dirigidos al equipo de ingeniería de INGEVIA. Palabras clave: Bigastro, CV-95, parasoles, zona de protección, dominio público, servidumbre, afección, línea límite de edificación, parcela edificable, Carreteras, ALCALAS ARIN.</t>
-  </si>
-  <si>
-    <t>Colaboración con PAVASAL EMPRESA CONSTRUCTORA, S.A. (Valencia) para la Cantera Peñalba, relativa a la definición técnica (geometría, marcas viales, señalización y drenaje) de un enlace/acceso de carretera compartido con un expediente paralelo de ampliación de extracción de áridos de Arenas Forna, S.L. (modificación del PGOU), en respuesta a un requerimiento de la Conselleria sobre un enlace ya aprobado en la tramitación de la Declaración de Interés Comunitario (DIC) de PAVASAL. El estudio de tráfico (actual y futuro, incluyendo el efecto de una nueva planta de aglomerado) lo elabora PAVASAL; INGEVIA se encarga de la definición geométrica del acceso, señalización y drenaje. El expediente incluye mapas de tráfico de la Conselleria, planos de propuesta de acceso (DWG) y el estudio de tráfico correspondiente. Los correos suelen proceder de PAVASAL (dominio @pavasal.com), dirigidos al equipo de ingeniería de INGEVIA. Palabras clave: Cantera Peñalba, PAVASAL, Arenas Forna, DIC, PGOU, enlace, acceso, CV-715, tráfico, IMD, Conselleria, drenaje, señalización.</t>
-  </si>
-  <si>
-    <t>Proyecto de Nacho Gadea (Ignacio Gadea, de Teproval, S.L.) para una electrolinera de recarga de vehículos eléctricos con usos complementarios, en la finca de La Llosa, desarrollado para Iberdrola/bp pulse (bajo el nombre comercial "Charging Together") y tramitado mediante una Declaración de Interés Comunitario (DIC) única que ampara todas las actividades desde el inicio. El expediente incluye el estudio de ubicación estratégica de la finca, los planos de implantación general del proyecto (planta general, en sucesivas versiones CAD/PDF), y la coordinación de accesos y presupuestos para la tramitación de la DIC e informes sectoriales. Los correos suelen proceder de Teproval (dominio @teproval.com) y de Iberdrola/bp pulse-Charging Together (dominio @chargingtogether.es), dirigidos al equipo de ingeniería de INGEVIA; también hay envíos de planos a colaboradores externos del proyecto. Palabras clave: La Llosa, Nacho Gadea, Teproval, electrolinera, DIC, Charging Together, Iberdrola, bp pulse, implantación, planta general, ubicación estratégica.</t>
-  </si>
-  <si>
-    <t>Proyecto de Nacho Gadea (Ignacio Gadea, de Teproval, S.L.) para el desarrollo de una electrolinera de recarga de vehículos eléctricos, gasolinera, parking y una posible campa de camiones (25.000 m²), en la finca A7 de Moncada (área también referida como Rafelbunyol), para Iberdrola/bp pulse (Charging Together). La tramitación se articula en fases: una Declaración de Interés Comunitario (DIC) de gasolinera ya en curso y una posible DIC de Fase II para el resto de usos, con consulta de accesos ante Fomento/Carreteras (expediente VLC-AUT-26-009-V1) y coordinación con el técnico municipal de Moncada. El expediente incluye sucesivas versiones de los planos de implantación (CAD/PDF), planos de parcelas marcadas y de la rotonda (con reparto de titularidad entre Ayuntamiento, Consellería/CV-32 y Ministerio), y presupuestos/ofertas para la tramitación de la DIC e informes sectoriales. Los correos suelen proceder de Teproval (dominio @teproval.com) y de Iberdrola/bp pulse-Charging Together (dominio @chargingtogether.es), dirigidos al equipo de ingeniería de INGEVIA; también hay envíos de planos a colaboradores externos del proyecto. Palabras clave: Moncada, Rafelbunyol, Nacho Gadea, Teproval, electrolinera, gasolinera, DIC, Fase II, Charging Together, Iberdrola, bp pulse, campa de camiones, rotonda, VLC-AUT-26-009.</t>
-  </si>
-  <si>
-    <t>Encargo relacionado con MEETPACK (fabricante de envases/embalajes decorados) en Benasau, tramitado a través de Raúl García Studio/Arquitectos (estudio de arquitectura encargado del Proyecto de Urbanización y su Declaración de Interés Comunitario, DIC), para la redacción del estudio de tráfico y accesos requerido en la subsanación del expediente del PU de Benasau. El expediente incluye la documentación de ordenación e instalaciones del proyecto de urbanización (planos DWG/PDF: ordenación, instalaciones, sección vial), datos de la actividad para el estudio de tráfico (parque de vehículos de trabajadores, tipología y volumen de camiones de suministro de materia prima y salida de mercancía), y los planos y el estudio de tráfico y accesos elaborados por INGEVIA. Los correos suelen proceder de Raúl García Studio/Arquitectos (dominio @raulgarcia-studio.com), dirigidos al equipo de ingeniería de INGEVIA. Palabras clave: Benasau, MEETPACK, Raúl García, Proyecto de Urbanización, PU, DIC, subsanación, estudio de tráfico, accesos, envases.</t>
-  </si>
-  <si>
-    <t>Encargo de Facundo García de la Cuadra Rubio (abogado, titular de la explotación agraria de la finca familiar "Masía del Algudor", representando a su padre José Manuel García de la Cuadra como propietario) para la tramitación de varias autorizaciones ante el Ministerio (Fomento), la Confederación Hidrográfica del Júcar (CHJ) e Iberdrola relativas a la finca: vallado perimetral de la propiedad, desbroce y limpieza de los márgenes de carretera, cerramiento con valla o bionda de tramos de carretera, desbroce de la servidumbre de paso de Iberdrola, y un proyecto de puente. El expediente incluye las solicitudes firmadas presentadas a cada organismo (cerramiento de carretera, vallado de finca, CHJ, desbroce e Iberdrola), así como la documentación y presentación remitidas a Fomento. Los correos suelen proceder directamente de Facundo García (facundogar@gmail.com), dirigidos al equipo de ingeniería de INGEVIA. Palabras clave: Facundo García, Masía del Algudor, Silla, vallado, desbroce, cerramiento, CHJ, Iberdrola, Fomento, servidumbre de paso, puente.</t>
-  </si>
-  <si>
-    <t>Encargo de Vestel Ingenieros, S.L.U. (ingeniería de movilidad eléctrica, Paterna) para un proyecto de MAN en Parets del Vallès (Barcelona), centrado en el estudio de trayectorias y radios de giro de vehículos (camiones y turismos) y la implantación de cargadores eléctricos/dispensadores y plazas de aparcamiento en la parcela. El expediente incluye el CAD de la parcela con la implantación de cargadores y plazas, planos de un paso fluvial (Ptge Fluvial), y la definición de dimensiones de las unidades de carga y de las plazas (incluida la configuración combinada camión/turismos). Los correos suelen proceder de Vestel Ingenieros (dominio @vestelingenieros.com), dirigidos al equipo de ingeniería de INGEVIA. Palabras clave: Parets del Vallès, MAN, Vestel Ingenieros, movilidad eléctrica, radios de giro, trayectorias, cargadores, plazas de aparcamiento, paso fluvial.</t>
-  </si>
-  <si>
     <t>01.-VILAMARXANT-POL ENCHILAGAR</t>
   </si>
   <si>
@@ -1282,128 +1225,191 @@
     <t>13.-CUENCA-NAVE</t>
   </si>
   <si>
-    <t>Carpeta interna de INGEVIA para estudios propios de parcelas y naves industriales detectadas en portales inmobiliarios (principalmente Idealista) como oportunidades de compra o desarrollo, en distintos municipios (Vilamarxant, Manises, Puçol, Catarroja, Cuenca, entre otros). Cada subcarpeta corresponde a un inmueble o parcela concreta, e incluye habitualmente el aviso de Idealista con los datos básicos del inmueble (precio, superficie, ubicación), el estudio catastral y de implantación (planos de estudio de implantación en CAD/PDF), y en algunos casos instrucciones internas para crear la carpeta correspondiente y generar el estudio (p.ej. planta con lavadero, polígono industrial). No hay un cliente externo: los correos son internos de INGEVIA (dominio @ingevia.com), normalmente iniciados por Miguel Vera y dirigidos al resto del equipo técnico. Palabras clave: INGEVIA-ESTUDIOS, estudio interno, Idealista, parcela, nave industrial, catastral, implantación, polígono, Vilamarxant, Manises, Puçol, Catarroja, Cuenca.</t>
-  </si>
-  <si>
-    <t>Estudio interno de INGEVIA sobre un terreno en venta en el polígono/paraje "Enchilagar" de Vilamarxant (anuncio de Idealista, terreno de 2.929 m², precio 80.000 €), a partir de un aviso reenviado por Miguel Vera para que el equipo técnico baje el plano catastral y prepare el estudio de viabilidad/implantación de la parcela. Los correos suelen ser internos de INGEVIA (dominio @ingevia.com) o notificaciones automáticas de Idealista (noresponder@idealista.com) reenviadas internamente. Palabras clave: Vilamarxant, Enchilagar, Idealista, terreno en venta, catastral, estudio de implantación.</t>
-  </si>
-  <si>
-    <t>Estudio interno de INGEVIA para una posible estación de servicio de la marca MIDES en Avda. Mas de l'Oli, 190 (Manises), consistente en la instrucción interna de crear la carpeta del expediente y generar la planta de implantación incluyendo un lavadero de coches. Los correos son internos de INGEVIA (dominio @ingevia.com), iniciados por Miguel Vera. Palabras clave: Manises, Avda Mas de l'Oli 190, MIDES, gasolinera, estación de servicio, lavadero, planta de implantación.</t>
-  </si>
-  <si>
-    <t>Estudio interno de INGEVIA para una posible implantación de la marca MIDES en el polígono industrial de Manises, en Avda. Mas de l'Oli, 17 (una parcela distinta de la estudiada en el nº190 de la misma avenida, dentro de la misma serie de estudios internos). El correo consiste en una instrucción interna de Miguel Vera para crear la carpeta del expediente ("Polígono Manises"), con imágenes de referencia de la ubicación/parcela adjuntas, sin texto adicional. Los correos son internos de INGEVIA (dominio @ingevia.com). Palabras clave: Manises, Avda Mas de l'Oli 17, polígono industrial, MIDES, estudio interno.</t>
-  </si>
-  <si>
-    <t>Estudio interno de INGEVIA sobre una posible parcela/nave en la calle Santos Justo y Pastor, dentro del polígono industrial de Manises (área referida internamente como "polígono aeropuerto", próxima al aeropuerto de Valencia-Manises), a partir de un correo interno de Miguel Vera con imágenes de referencia de la ubicación adjuntas, sin texto adicional. Los correos son internos de INGEVIA (dominio @ingevia.com). Palabras clave: Manises, Santos Justo y Pastor, polígono aeropuerto, estudio interno.</t>
-  </si>
-  <si>
-    <t>Estudio interno de INGEVIA (estudio de implantación y plano catastral) para una parcela situada en el Camí Llíria - Magraners, en Puçol, dentro de la misma serie de estudios internos de oportunidades de suelo. El expediente contiene el estudio de implantación con el plano catastral (PDF) y el correspondiente archivo CAD (DWG), enviados por Miguel Vera como correspondencia saliente del despacho — a diferencia de los otros casos, aquí no hay un correo entrante de origen (aviso de Idealista o instrucción), solo la salida del estudio ya elaborado. Palabras clave: Puçol, Camí Llíria, Magraners, estudio de implantación, catastral, estudio interno.</t>
-  </si>
-  <si>
-    <t>Estudio interno de INGEVIA (estudio de implantación) para una parcela situada en Ronda Nord, en Catarroja, dentro de la misma serie de estudios internos de oportunidades de suelo. El expediente contiene únicamente el archivo CAD (DWG) del estudio de implantación, enviado por Miguel Vera como correspondencia saliente del despacho, sin correo de origen ni documentación adicional. Palabras clave: Catarroja, Ronda Nord, estudio de implantación, estudio interno, DWG.</t>
-  </si>
-  <si>
-    <t>Estudio interno de INGEVIA sobre una nave industrial en venta en Cuenca (anuncio de Idealista: 430.000 €, 850 m² construidos / 700 m² útiles, segunda mano en buen estado, 2 baños), a partir de un aviso reenviado por Miguel Vera con instrucción de crear la carpeta y descargar la información del inmueble. Los correos suelen ser internos de INGEVIA (dominio @ingevia.com) o notificaciones automáticas de Idealista (noresponder@idealista.com) reenviadas internamente. Palabras clave: Cuenca, nave industrial, Idealista, nave en venta, estudio interno.</t>
-  </si>
-  <si>
-    <t>Encargo de Amadeo Delhom para la elaboración de un informe relativo a una Unidad de Ejecución (UE) en Albal, a partir de la normativa urbanística aportada por el cliente sobre edificación, altura y casco urbano (extracto del Plan General, PGOU). El expediente incluye el recorte/documento normativo remitido por el cliente como base para el informe que ha de redactar INGEVIA. Los correos suelen proceder directamente de Amadeo Delhom (prodelhom@gmail.com), dirigidos al equipo de ingeniería de INGEVIA. Palabras clave: Albal, UE Delhom, Unidad de Ejecución, PGOU, edificación, altura, casco urbano, informe.</t>
-  </si>
-  <si>
-    <t>Colaboración de INGEVIA con el Ayuntamiento de Torrent para trabajos de ingeniería civil vinculados a la reconstrucción de infraestructuras urbanas tras la DANA, tramitados mediante contratos menores. El encargo puede abarcar distintas actuaciones y zonas del municipio (cada una en su propia subcarpeta), incluyendo memorias valoradas subvencionables, proyectos, dirección de obra (DO), coordinación de seguridad y salud (CSS) y trabajos topográficos. Los correos suelen proceder del Ayuntamiento de Torrent (dominio @torrent.es), dirigidos al equipo de ingeniería de INGEVIA. Palabras clave: Ayuntamiento de Torrent, DANA, reconstrucción, memoria valorada, contrato menor, DO, CSS, topografía.</t>
-  </si>
-  <si>
-    <t>Actuación 3 de reconstrucción de la zona urbana de La Venteta y El Pantano (Torrent) tras la DANA, con un presupuesto de referencia de aprox. 3,23 millones de euros, que incluye el encauzamiento Mas del Jutge-La Curra, la reparación de viales de la urbanización Mas del Jutge-La Curra, el alumbrado público de la calle Ávila y del área recreativa El Pantà, la restitución de jardinería de la zona del pantano, y las asistencias técnicas asociadas (memoria valorada, proyecto, dirección de obra y CSS, y topografía). El expediente incluye la memoria valorada subvencional (documento de la actuación 3) y la solicitud de oferta económica del Ayuntamiento para contratarla como contrato menor. Los correos suelen proceder del Ayuntamiento de Torrent (dominio @torrent.es), dirigidos al equipo de ingeniería de INGEVIA. Palabras clave: La Venteta, El Pantano, Torrent, DANA, actuación 3, Mas del Jutge-La Curra, memoria valorada, contrato menor.</t>
-  </si>
-  <si>
-    <t>Encargo de INGEVIA como Dirección de Obra (DO) para la construcción de nuevas estaciones de servicio desatendidas de PLENERGY (marca comercial Plenoil), coordinado en el día a día con PLAINCO (empresa de gestión de proyectos que actúa de intermediaria técnica). Cada estación corresponde a una "US" (Unidad de Suministro) numerada, ubicada en un municipio distinto, con su propia subcarpeta. El expediente típico de cada estación incluye: planos de implantación y de cámaras de videovigilancia, el proyecto e instalación eléctrica de baja tensión (BT) y su tramitación ante el OCA (Organismo de Control Autorizado)/Industria, propuestas mecánicas y de depósitos, el Plan de Seguridad y Salud (PSS), el acta de replanteo y la convocatoria de inicio de obra, checklists de remates finales, y —en parcelas que ya albergaban una gasolinera anterior— trabajos de remediación ambiental del suelo. Los correos suelen proceder de PLENERGY (dominio @plenergy.es) y de PLAINCO (dominio @plainco.es), dirigidos al equipo de ingeniería de INGEVIA; también intervienen subcontratistas puntuales (instaladores eléctricos, empresas de remediación, fabricantes de equipos). Palabras clave: PLENERGY, Plenoil, PLAINCO, Dirección de Obra, DO, estación de servicio, US (Unidad de Suministro), OCA, BT, remediación, PSS, acta de replanteo.</t>
-  </si>
-  <si>
     <t>Estación de servicio Plenoil US 463, en Ctra. del Pla 148, Valls (Tarragona). El expediente incluye la ficha técnica de luminarias, el Certificado de Instalación Eléctrica (CIE) para el suministro eléctrico definitivo, el checklist de repaso de remates finales de obra, y los planos actualizados. Palabras clave: Valls, Tarragona, US463, CIE, suministro eléctrico, remates, luminarias.</t>
   </si>
   <si>
-    <t>Estación de servicio Plenoil US 336, en Av. Valencia-Barna 60, Vinaroz — fase de demolición de la instalación previa antes de construir la nueva estación. Incluye la primera factura de Plenoil y la certificación del 25% del total para el inicio de obra. Palabras clave: Vinaroz, US336, demolición, factura, certificación inicio de obra.</t>
-  </si>
-  <si>
-    <t>Estación de servicio Plenoil US 539, en Ctra. Valencia 75, Riba-roja de Turia. Incluye la autorización municipal de ocupación de vía pública (OVP) para contenedor de obra, la inspección OCA de la instalación industrial de baja tensión (IIBT), las propuestas de depósitos y su modificación (nuevos tanques de 40.000 y 30.000 litros), y las propuestas de instalación eléctrica y mecánica. Palabras clave: Riba-roja de Turia, US539, OVP, OCA, IIBT, depósitos, instalación mecánica.</t>
-  </si>
-  <si>
-    <t>Estación de servicio Plenoil US 513, en Av. Costa Blanca 9 (Noguera), Ondara. Incluye la planificación e implantación de obra, el plano de cámaras de videovigilancia, la consulta sobre alineaciones de la parcela, el proyecto eléctrico de baja tensión firmado y su certificado, y el programa de comprobación de la Entidad de Inspección y Control (EIC). Palabras clave: Ondara, US513, implantación, alineaciones, proyecto eléctrico, EIC.</t>
-  </si>
-  <si>
-    <t>Estación de servicio Plenoil US 552 (conocida internamente como "Tamos"), en Av. Ramón Menéndez Pidal 58, Albacete. Incluye el proyecto eléctrico de baja tensión para su tramitación ante OCA, el esquema unifilar del CGBT, un requerimiento de Industria, y un escrito de alegaciones frente a una resolución de precinto/cierre de las instalaciones — este emplazamiento ha tenido un conflicto administrativo relevante. Palabras clave: Albacete, US552, Tamos, OCA, CGBT, requerimiento Industria, precinto, alegaciones.</t>
-  </si>
-  <si>
-    <t>Estación de servicio Plenoil US 534, en Av. Mediterrani 16, Canet d'en Berenguer. Incluye la inspección de la instalación de baja tensión, el esquema unifilar en CAD, los planos de implantación de obra, y la gestión de cargadores eléctricos y contador con Iberdrola. Palabras clave: Canet d'en Berenguer, US534, unifilar, implantación, cargadores eléctricos, Iberdrola.</t>
-  </si>
-  <si>
-    <t>Estación de servicio Plenoil US 536, en Av. Reyes Católicos 68, Cuenca. Incluye la planificación y adjudicación de la obra, la coordinación de cargadores eléctricos y contador con Iberdrola, los trabajos e infraestructuras de remediación ambiental del suelo (AVIA), el proyecto eléctrico y la propuesta de instalación mecánica. Palabras clave: Cuenca, US536, adjudicación, remediación, AVIA, Iberdrola, proyecto eléctrico.</t>
-  </si>
-  <si>
-    <t>Estación de servicio Plenoil US 303A, en Ctra. de Valencia Km 8,8, Cuarte de Huerva (Zaragoza) — parcela adquirida de una antigua estación de servicio ("E.S. Santa Fe"). Incluye la oferta de remediación ambiental (EHS Techniques), la visita inicial de obra, la solicitud de inspección de baja tensión, el esquema unifilar y la propuesta de usos/distribución de la parcela. Palabras clave: Cuarte de Huerva, Zaragoza, US303A, adquisición, E.S. Santa Fe, remediación, EHS Techniques, inspección BT.</t>
-  </si>
-  <si>
-    <t>Estación de servicio Plenoil US 584, en Calle Acequia del Río 37, Formentera del Segura. Incluye la convocatoria de la visita inicial de obra y la firma del acta de replanteo, el plano de implantación y de cámaras, el Plan de Seguridad y Salud (PSS, de MADIC), las conversaciones con el técnico municipal, y el proyecto eléctrico de baja tensión. Palabras clave: Formentera del Segura, US584, acta de replanteo, PSS, MADIC, técnico municipal, proyecto eléctrico.</t>
-  </si>
-  <si>
-    <t>Estación de servicio Plenoil US 574, en Calle Núm. Ocho 7, Albal (polígono Peymon). Incluye la convocatoria de inicio de obra y la firma del acta de replanteo, el plano de implantación, el proyecto eléctrico de baja tensión, y la propuesta de instalación mecánica (JUVACAR, enviada junto con la estación de Cuenca). Palabras clave: Albal, Peymon, US574, acta de replanteo, implantación, proyecto eléctrico, JUVACAR.</t>
-  </si>
-  <si>
-    <t>Encargo de INGEVIA para PLENERGY SL (marca comercial Plenoil) en la fase de redacción de proyecto, adquisición/due diligence y tramitación de licencias de nuevas estaciones de servicio, previa a la fase de construcción (que se gestiona aparte en la carpeta "DO PLENERGY"). Cada estación corresponde a una "US" numerada, en un municipio distinto, con su propia subcarpeta; varias de ellas son adquisiciones o reformas de estaciones de servicio de otras marcas (p. ej. BP) que se transforman en Plenoil. El expediente típico de cada estación incluye: el bloque de encargo (nota simple, informe urbanístico, catastro, estudio económico), el plano de implantación y sus sucesivas versiones, observaciones técnicas y proyecto de licitación/visado, informes de viabilidad urbanística y licencias (demolición, ambiental, obra menor), presupuestos y mediciones (BC3/Presto), planos de cámaras/PIC de elementos, y ofertas de equipamiento (p. ej. informática de surtidores con Alvic). Los correos suelen proceder de PLENERGY (dominio @plenergy.es, equipo de la Oficina Técnica de Proyectos), dirigidos al equipo de ingeniería de INGEVIA. Palabras clave: PLENERGY, Plenoil, US (Unidad de Suministro), proyecto, licencias, due diligence, implantación, adquisición, reforma.</t>
-  </si>
-  <si>
-    <t>Estudio inicial de accesos para la futura estación de servicio Plenergy en Camí de Faitanar 2, Picanya (fase de proyecto, sin código US asignado aún). A partir del plano de implantación en CAD facilitado por PLAINCO, INGEVIA ha de estudiar el acceso a la parcela para solicitar el informe de viabilidad de accesos a la Conselleria. El expediente incluye el CAD de implantación y el plano de acceso a la parcela. Los correos suelen proceder de PLAINCO (dominio @plainco.es), dirigidos al equipo de ingeniería de INGEVIA. Palabras clave: Picanya, Camí de Faitanar, accesos, viabilidad, Conselleria, PLAINCO, implantación.</t>
-  </si>
-  <si>
-    <t>Estación de servicio Plenergy US 552 ("Tamos"), en Av. Ramón Menéndez Pidal 58, Albacete — antigua estación de TAMOS SA que se adquiere y remodela para su conversión a la marca Plenoil. El expediente incluye el informe de diligencia previo a la adquisición (E.S. Albacete Tamos, de PLAINCO), el proyecto de remodelación (recuperando los depósitos existentes, con 3,5 surtidores), los planos de implantación y cámaras, el esquema unifilar y presupuesto eléctrico, y la documentación de un procedimiento administrativo relevante del Ayuntamiento: la resolución de paralización de obra e inicio de procedimiento de restauración de la legalidad (expediente 1588866J) contra TAMOS SA. Los correos suelen proceder de PLENERGY y PLAINCO (dominios @plenergy.es y @plainco.es), dirigidos al equipo de ingeniería de INGEVIA. Palabras clave: Albacete, US552, Tamos, TAMOS SA, remodelación, paralización, restauración de la legalidad, PLAINCO.</t>
-  </si>
-  <si>
-    <t>Proyecto completo de nueva construcción de la estación de servicio Plenoil US 188A, en Calle Sant Ramón 39-51, El Campello. El expediente es el más extenso de la serie e incluye: la escritura de agrupación de parcelas, la tramitación de la cédula/certificado de compatibilidad urbanística (CCU) ante el Ayuntamiento (con reinicio de expediente), el levantamiento topográfico (repetido tras resultar insuficiente el primero) y el estudio geotécnico, el proyecto técnico multidisciplinar completo y visado (implantación, estructura, saneamiento, red de agua, protección contra incendios, instalación eléctrica, caseta, tótem y elementos de seguridad/CCTV), las observaciones técnicas y los sucesivos requerimientos documentales y técnicos de Addient (entidad revisora externa), la tramitación de la acometida eléctrica con Iberdrola (distribuidora, definitivo, TCT), y el anejo de estudio de gestión de residuos. Los correos suelen proceder de PLENERGY/PLAINCO (dominios @plenergy.es y @plainco.es), dirigidos al equipo de ingeniería de INGEVIA. Palabras clave: El Campello, US188A, San Ramón, cédula urbanística, CCU, geotécnico, topográfico, Addient, Iberdrola, proyecto visado.</t>
-  </si>
-  <si>
-    <t>Proyecto de nueva construcción (demolición y reconstrucción) de la estación de servicio Plenoil US 235, en Callejón del Sol 10, Orihuela. El expediente incluye la licencia de demolición de la edificación previa, el certificado de compatibilidad urbanística y el informe de viabilidad urbanística (ECUV), el acta de alineaciones y rasantes, las sucesivas versiones del plano de implantación, las observaciones y requerimiento técnico —incluida una discusión específica sobre el cumplimiento normativo de fachadas y cubierta (teja árabe sobre estructura metálica, pendiente de cubierta)—, los preciarios en marquesina/fachada, el presupuesto y mediciones (BC3/Presto), el plano de cámaras, y la solicitud de un estudio lumínico externo (ASVITAE) para el alumbrado. Los correos suelen proceder de PLENERGY y PLAINCO (dominios @plenergy.es y @plainco.es), dirigidos al equipo de ingeniería de INGEVIA. Palabras clave: Orihuela, US235, demolición, viabilidad urbanística, fachadas, teja árabe, preciarios, alumbrado, ASVITAE.</t>
-  </si>
-  <si>
-    <t>Proyecto de remodelación de la estación de servicio Plenoil US 574, en Calle Núm. Ocho 7, Albal (polígono Peymon) — estación existente adquirida/arrendada y reformada para su conversión a Plenoil. El expediente incluye el contrato de arrendamiento y licencias de la finca, el informe y bloque de documentación de la unidad (huella, solicitud de cesión urbanística, observaciones técnicas), el levantamiento topográfico, los planos de implantación, señalética, tótem y estado actual, una valoración con una versión de caseta reducida, el proyecto de remodelación y su presupuesto (incluyendo el capítulo de obra civil del edificio), el plano de cámaras, la tramitación de la licencia ambiental (acuerdo de la Junta de Gobierno Local) y el certificado de actividad para la apertura. Los correos suelen proceder de PLENERGY y PLAINCO (dominios @plenergy.es y @plainco.es), dirigidos al equipo de ingeniería de INGEVIA. Palabras clave: Albal, Peymon, US574, arrendamiento, remodelación, licencia ambiental, certificado de actividad, caseta reducida.</t>
-  </si>
-  <si>
-    <t>Adquisición y remodelación de la antigua estación E.S. Los Palacios (Tecnorojales, S.L.) en Calle Acequia del Río 37, Formentera del Segura, para su conversión a Plenoil (US 584 en fase de construcción). El expediente incluye el contrato de arrendamiento y nota simple de la finca, el bloque completo de due diligence (licencias y registro de instalación petrolífera, documentos técnicos —descontaminación, prueba de estanqueidad, venteos—, suministros, informes fiscal/laboral/operaciones), la documentación de cambio de titularidad de la actividad (con DNI del representante), la valoración de la estación, y el proyecto de remodelación con sus sucesivas versiones del plano de implantación, presupuesto y preciario. Los correos suelen proceder de PLENERGY/PLAINCO (dominios @plenergy.es y @plainco.es), dirigidos al equipo de ingeniería de INGEVIA. Palabras clave: Formentera del Segura, Los Palacios, Tecnorojales, due diligence, cambio de titularidad, remodelación, US584.</t>
-  </si>
-  <si>
-    <t>Adquisición y remodelación de la antigua estación E.S. Truyols en Ctra. Sabadell 1, Castellar del Vallès, para su conversión a Plenoil (US 585). El expediente sigue el flujo de trabajo estándar de adquisición (bloque de encargo con nota simple, catastro, estudio económico, huella, informe urbanístico y observaciones técnicas; plano de implantación, topográfico, señalética, tótem y estado actual), e incluye la solicitud y oferta de equipamiento informático de surtidores a Alvic, tramitada conjuntamente con las estaciones de Terrassa (US 586) y Coll de Nargó (US 588). También recoge el plano de cámaras y sucesivas modificaciones del preciario. Los correos suelen proceder de PLENERGY (dominio @plenergy.es) y de proveedores como Alvic (dominio @alvic.net), dirigidos al equipo de ingeniería de INGEVIA. Palabras clave: Castellar del Vallès, US585, E.S. Truyols, Alvic, adquisición, bloque de encargo, preciario.</t>
-  </si>
-  <si>
-    <t>Adquisición y remodelación de la antigua estación BP (E.S. Trevol) en Av. Santa Eulalia 39, Terrassa, para su conversión a Plenoil (US 586) — con referencias a una licencia ambiental no vigente asociada a una reforma previa de la estación BP en Passeig del Vint-i-dos de Juliol, 26. El expediente sigue el flujo estándar de adquisición (bloque de encargo con nota simple, catastro, estudio económico, huella, informe urbanístico y observaciones técnicas; plano de implantación —incluida una versión sin lavadero—, topográfico, señalética, tótem y estado actual), e incluye trámites compartidos con las estaciones de Castellar del Vallès (US 585) y Coll de Nargó (US 588): oferta de equipamiento informático (Alvic), PIC de elementos y modificaciones del preciario. También se tramita, de forma independiente, una licencia municipal menor específica para el lavadero. Los correos suelen proceder de PLENERGY (dominio @plenergy.es) y de proveedores como Alvic (dominio @alvic.net), dirigidos al equipo de ingeniería de INGEVIA. Palabras clave: Terrassa, US586, E.S. Trevol, BP, Alvic, licencia ambiental, lavadero, adquisición.</t>
-  </si>
-  <si>
-    <t>Encargos de CONSUM S. Coop. V. (cooperativa de supermercados) y de franquiciados de su formato Charter, para estudios de movilidad, accesos y aparcamiento vinculados a la apertura o reforma de tiendas en distintos municipios españoles. Cada emplazamiento/tienda tiene su propia subcarpeta. El expediente típico incluye: estudios de movilidad para la tramitación urbanística (modificaciones de POUM, proyectos de urbanización/reparcelación), estudios y mejora de accesos a la parcela, distribución de planta para nuevas aperturas, datos de ocupación de aparcamiento y tráfico de la tienda (a veces comparando con tiendas similares ya en funcionamiento), y estudios para la exención de plazas de aparcamiento (apoyados en informes de ventas y afluencia de clientes de proximidad). Los correos suelen proceder de CONSUM (dominio @consum.es) y, en el caso de tiendas Charter, de las sociedades franquiciadas/gestoras (p. ej. JJ Matriz Capital), dirigidos al equipo de ingeniería de INGEVIA. Palabras clave: CONSUM, Charter, estudio de movilidad, accesos, aparcamiento, apertura de tienda, POUM.</t>
-  </si>
-  <si>
-    <t>Apertura de una nueva tienda Consum en Calle del Forn Vicente Roca Cervera, 33, Xirivella. Incluye el plano de distribución de planta de la nueva tienda y los datos de ocupación de aparcamiento solicitados para el estudio de movilidad. Palabras clave: Xirivella, apertura, distribución de planta, aparcamiento.</t>
-  </si>
-  <si>
-    <t>Sin contenido sustantivo en el archivo enviado; solo un archivo de miniaturas del sistema. No hay base para una descripción todavía.</t>
-  </si>
-  <si>
-    <t>Estudio de mejora de accesos a la parcela de una tienda Consum en Calle Doctor Fleming 1E, El Viso de San Juan (Toledo). Incluye la ficha catastral y localización de la parcela, la opción de diseño de acceso preferida por el cliente, y el CAD correspondiente. Palabras clave: El Viso de San Juan, Toledo, accesos, catastro.</t>
-  </si>
-  <si>
-    <t>Estudio de movilidad para una tienda Consum en L'Arboç (Tarragona), en el marco de una modificación puntual del POUM y de los proyectos de urbanización y reparcelación del sector. Incluye la memoria completa y documentación de entrada de la modificación del POUM, los proyectos de urbanización y reparcelación, y los planos remitidos a Consum para la apertura. Palabras clave: L'Arboç, POUM, urbanización, reparcelación, estudio de movilidad.</t>
-  </si>
-  <si>
-    <t>Estudio de movilidad para una posible tienda Consum "Cinco Pinos" en Mollet del Vallès, finalmente no llevada a cabo (marcada "NO"). Incluye el checklist definitivo del estudio y los datos de tráfico y afluencia de la tienda Consum ya existente en Mollet del Vallès (T-1022), usados como referencia comparativa por tener un entorno similar. Palabras clave: Mollet del Vallès, Cinco Pinos, estudio de movilidad, descartado.</t>
-  </si>
-  <si>
-    <t>Tienda Charter (formato franquiciado de Consum) en Alboraia, gestionada por la sociedad Superfast Vacor, S.L. Incluye los datos de la sociedad gestora (remitidos por JJ Matriz Capital) y la oferta del estudio de movilidad para la apertura. Palabras clave: Alboraia, Charter, Superfast Vacor, JJ Matriz Capital, estudio de movilidad.</t>
-  </si>
-  <si>
-    <t>Estudio para la exención de plazas de aparcamiento de la tienda Consum T-137 en Valencia (Olivereta). Incluye los planos del estado actual y de la propuesta, y los informes de ventas de proximidad y de afluencia/pasos de clientes utilizados para justificar la exención. Palabras clave: Olivereta, T-137, exención de aparcamiento, ventas de proximidad, afluencia de clientes.</t>
+    <t>AYTO TORRENT (@torrent.es). Reconstrucción tras DANA, contratos menores: memoria valorada, proyecto, Dirección de Obra (DO), CSS, topografía. Subcarpetas por actuación/zona del municipio.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONSUM (@consum.es) y tiendas Charter (franquicias, ej. JJ Matriz Capital). Estudios de movilidad, accesos, aparcamiento, POUM, apertura/reforma de tiendas. Subcarpeta por tienda.
+CONSUM (@consum.es) y tiendas Charter (franquicias, ej. JJ Matriz Capital). Estudios de movilidad, accesos, aparcamiento, POUM, apertura/reforma de tiendas. Subcarpeta por tienda.
+</t>
+  </si>
+  <si>
+    <t>CONSUM (@consum.es) y tiendas Charter (franquicias, ej. JJ Matriz Capital). Estudios de movilidad, accesos, aparcamiento, POUM, apertura/reforma de tiendas. Subcarpeta por tienda.</t>
+  </si>
+  <si>
+    <t>PLENERGY (@plenergy.es, Oficina Técnica) - FASE PROYECTO/ADQUISICIÓN, previa a obra (no DO). Due diligence, licencias, catastro, implantación, visado, BC3. Código US por estación.</t>
+  </si>
+  <si>
+    <t>DO PLENERGY (@plenergy.es + PLAINCO @plainco.es) - FASE CONSTRUCCIÓN (Dirección de Obra, posterior a fase proyecto). OCA, BT, PSS, acta de replanteo, remediación. Código US por estación.</t>
+  </si>
+  <si>
+    <t>Amadeo Delhom (prodelhom@gmail.com). Informe sobre Unidad de Ejecución (UE) en Albal: normativa PGOU, edificación, altura, casco urbano.</t>
+  </si>
+  <si>
+    <t>PAVASAL (@pavasal.com), Cantera Peñalba. Enlace/acceso carretera compartido con Arenas Forna (PGOU). DIC, tráfico, señalización, drenaje, Conselleria, CV-715.</t>
+  </si>
+  <si>
+    <t>Nacho Gadea/Teproval (@teproval.com) + Iberdrola/bp pulse-Charging Together (@chargingtogether.es). Electrolinera+gasolinera+parking, finca A7 Moncada/Rafelbunyol. DIC, Fase II, rotonda, VLC-AUT-26-009.</t>
+  </si>
+  <si>
+    <t>MEETPACK (envases) en Benasau, vía Raúl García Studio (@raulgarcia-studio.com). Proyecto Urbanización, DIC, subsanación: estudio de tráfico y accesos.</t>
+  </si>
+  <si>
+    <t>Vestel Ingenieros (@vestelingenieros.com), movilidad eléctrica. Proyecto MAN en Parets del Vallès: radios de giro, trayectorias, cargadores eléctricos, plazas aparcamiento, paso fluvial.</t>
+  </si>
+  <si>
+    <t>INGEVIA-ESTUDIOS: estudios internos (@ingevia.com, M. Vera) de parcelas/naves de Idealista, sin cliente externo. Catastral, implantación, polígono. Vilamarxant, Manises, Puçol, Catarroja, Cuenca.</t>
+  </si>
+  <si>
+    <t>Facundo García (facundogar@gmail.com), finca Masía del Algudor, Silla. Autorizaciones a Fomento, CHJ e Iberdrola: vallado, desbroce, cerramiento carretera, servidumbre de paso, puente.</t>
+  </si>
+  <si>
+    <t>ALCALAS ARIN (@alcalas.es), Bigastro, CV-95. Parasoles en parcela; zona de protección de carretera (dominio público, servidumbre, afección, línea edificación), parcela edificable.</t>
+  </si>
+  <si>
+    <t>Voladores de Levante (marcossrealm@gmail.com), San Antonio de Benagéber. Greenfield. Memoria Informativa Actividad en Terreno, parcelas, Servicio Territorial de Carreteras.</t>
+  </si>
+  <si>
+    <t>FENIX GESTION (fenixgestion@outlook.es), gasolinera Serra. DIC (licencia carburantes): ampliación/prórroga, compraventa, cambio titularidad, Consellería, Ayuntamiento.</t>
+  </si>
+  <si>
+    <t>Ferrovial Energía (@ferrovial.com) + MG Desarrollos (@desarrollosmg.es). Fotovoltaica sobre aparcamiento, San Fernando/Maspalomas. Topográfico, báculo, pórtico, LONGi.</t>
+  </si>
+  <si>
+    <t>GABTECO + Tragsa/Tragsatec + Ayto Quart de Poblet. Reparación caminos/viales rurales (DANA), Quart de Poblet. RP VIALES, memoria valorada, CHJ, vados, Tragsa.</t>
+  </si>
+  <si>
+    <t>SARRIÓN (Estaciones de Servicio Hermanos Sarrión S.L.), Requena. Gestiones técnicas, proyectos ingeniería/arquitectura, licencias e intervenciones urbanísticas, estaciones de servicio.</t>
+  </si>
+  <si>
+    <t>DAYHE, Nuevo Centro (Valencia). Modificación Puntual Plan General (MPG), estudio de tráfico y movilidad, presupuesto. Gestiones con Encarna.</t>
+  </si>
+  <si>
+    <t>PAI GINERMARK, Rotglà i Corberà. Programa Actuación Integrada (PAI): topográfico, planta base, perfiles longitudinales CAD/DWG. Interlocutor: Joan Giner.</t>
+  </si>
+  <si>
+    <t>PALMETILLO, Alcalá de Guadaíra. Análisis catastral/urbanístico: normativa Plan Parcial, alturas, alineaciones y rasantes. Gestión: David Reyero (Reyqueda).</t>
+  </si>
+  <si>
+    <t>ZONA LOGÍSTICA, La Bisbal. Estudio de viabilidad técnica/urbanística para almacén/nave logística; planos CAD de implantación (DWG). Interlocutor: Concepción Salmerón.</t>
+  </si>
+  <si>
+    <t>SOCUHER, La Torreta. Presupuestos técnicos/ofertas para estación de servicio desatendida (gasolinera automática). Interlocutor: José Luis Quesada.</t>
+  </si>
+  <si>
+    <t>DIC, Alfinach (Puzol). Trámite ante GVA: copia, certificación de vigencia e informes de la Declaración de Interés Comunitario (DIC). Rep.: Claudio Partearroyo, Miguel Vera.</t>
+  </si>
+  <si>
+    <t>ENCARNA BOSCH, Nuevo Centro (Valencia) — edificio comercial. PGOU/MPG, topográfico y CAD (DWG), estudio de tráfico/movilidad, pistas de pádel en cubierta.</t>
+  </si>
+  <si>
+    <t>Actuación 3, Torrent: reconstrucción La Venteta y El Pantano tras DANA (~3,23M€). Encauzamiento Mas del Jutge-La Curra, viales, alumbrado C/Ávila y El Pantà, jardinería, memoria valorada, DO, CSS, topografía. @torrent.es.</t>
+  </si>
+  <si>
+    <t>Consum Xirivella (C/ Forn Vicente Roca Cervera 33): apertura nueva tienda. Distribución de planta, datos de ocupación de aparcamiento para estudio de movilidad.</t>
+  </si>
+  <si>
+    <t>CONSUM-CHARTER Castellón: sin contenido sustantivo (solo archivo de miniaturas). Sin base para descripción todavía.</t>
+  </si>
+  <si>
+    <t>Consum El Viso de San Juan (Toledo), C/ Doctor Fleming 1E: mejora de accesos a parcela. Ficha catastral, localización, opción de acceso preferida, CAD.</t>
+  </si>
+  <si>
+    <t>Consum L'Arboç (Tarragona): estudio de movilidad. Modificación puntual POUM, proyectos de urbanización y reparcelación, planos remitidos para apertura.</t>
+  </si>
+  <si>
+    <t>Consum Mollet del Vallès "Cinco Pinos": estudio de movilidad, finalmente descartado (NO). Checklist definitivo; datos tráfico/afluencia de tienda existente T-1022 como referencia.</t>
+  </si>
+  <si>
+    <t>Consum Charter Alboraia (franquicia), gestionada por Superfast Vacor S.L. (datos vía JJ Matriz Capital). Oferta de estudio de movilidad para la apertura.</t>
+  </si>
+  <si>
+    <t>Consum T-137 Olivereta (Valencia): estudio para exención de plazas de aparcamiento. Planos estado actual/propuesta, informes de ventas de proximidad y afluencia de clientes.</t>
+  </si>
+  <si>
+    <t>Plenergy Picanya, Camí de Faitanar 2 (fase proyecto, sin US aún). Estudio inicial de accesos a parcela para informe de viabilidad ante Conselleria. CAD implantación. PLAINCO (@plainco.es).</t>
+  </si>
+  <si>
+    <t>Plenergy US552 "Tamos", Albacete — adquisición y remodelación de antigua TAMOS SA. Due diligence, 3,5 surtidores, unifilar/presupuesto eléctrico, resolución paralización obra (exp. 1588866J). @plenergy.es, @plainco.es.</t>
+  </si>
+  <si>
+    <t>Plenoil US188A, El Campello (C/ Sant Ramón). Nueva construcción completa: agrupación parcelas, cédula urbanística (CCU), topográfico, geotécnico, proyecto visado multidisciplinar, requerimientos Addient, acometida Iberdrola, residuos.</t>
+  </si>
+  <si>
+    <t>Plenoil US235, Orihuela (Callejón del Sol 10). Demolición y reconstrucción: licencia demolición, viabilidad urbanística (ECUV), alineaciones/rasantes, fachadas/teja árabe, BC3/Presto, alumbrado ASVITAE.</t>
+  </si>
+  <si>
+    <t>Plenoil US574, Albal-Peymon (fase proyecto). Adquisición/arrendamiento y remodelación estación existente: bloque de encargo, topográfico, implantación, caseta reducida, licencia ambiental, certificado actividad.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plenoil US584, Formentera del Segura. Adquisición y remodelación de antigua E.S. Los Palacios (Tecnorojales): due diligence, descontaminación/estanqueidad, cambio titularidad, valoración, implantación.
+</t>
+  </si>
+  <si>
+    <t>Plenoil US585, Castellar del Vallès. Adquisición y remodelación de antigua E.S. Truyols: bloque de encargo, implantación, informática Alvic (compartido con Terrassa US586 y Coll de Nargó US588), preciario.</t>
+  </si>
+  <si>
+    <t>Plenoil US586, Terrassa (Av. Sta Eulalia). Adquisición/remodelación de antigua BP (E.S. Trevol); licencia ambiental no vigente. Compartido con Castellar US585 y Coll de Nargó US588: Alvic, PIC, preciario. Licencia lavadero aparte.</t>
+  </si>
+  <si>
+    <t>Plenoil US463, Valls (Tarragona). Luminarias, Certificado Instalación Eléctrica (CIE) suministro definitivo, checklist remates finales, planos actualizados.</t>
+  </si>
+  <si>
+    <t>Plenoil US336, Vinaroz. Fase demolición instalación previa antes de construir. Primera factura Plenoil, certificación 25% inicio de obra.</t>
+  </si>
+  <si>
+    <t>Plenoil US539, Riba-roja de Turia. OVP contenedor obra, inspección OCA (IIBT), depósitos nuevos (40.000/30.000L), propuestas eléctrica y mecánica.</t>
+  </si>
+  <si>
+    <t>Plenoil US513, Ondara. Planificación/implantación obra, plano cámaras, alineaciones parcela, proyecto eléctrico BT firmado+certificado, programa EIC.</t>
+  </si>
+  <si>
+    <t>DO Plenoil US552 "Tamos", Albacete (fase construcción). Proyecto eléctrico BT para OCA, unifilar CGBT, requerimiento Industria, alegaciones vs. resolución de precinto/cierre — conflicto administrativo.</t>
+  </si>
+  <si>
+    <t>DO Plenoil US534, Canet d'en Berenguer. Inspección BT, unifilar CAD, planos de implantación de obra, cargadores eléctricos y contador con Iberdrola.</t>
+  </si>
+  <si>
+    <t>DO Plenoil US536, Cuenca. Planificación y adjudicación de obra, cargadores eléctricos+contador Iberdrola, remediación ambiental del suelo (AVIA), proyecto eléctrico, propuesta mecánica.</t>
+  </si>
+  <si>
+    <t>DO Plenoil US303A, Cuarte de Huerva (Zaragoza). Adquisición de antigua E.S. Santa Fe: remediación (EHS Techniques), visita inicial de obra, inspección BT, unifilar, propuesta de usos.</t>
+  </si>
+  <si>
+    <t>DO Plenoil US584, Formentera del Segura (fase construcción). Convocatoria/acta de replanteo, implantación, cámaras, PSS (MADIC), técnico municipal, proyecto eléctrico BT.</t>
+  </si>
+  <si>
+    <t>DO Plenoil US574, Albal-Peymon (fase construcción). Convocatoria/acta de replanteo, implantación, proyecto eléctrico BT, propuesta mecánica JUVACAR (compartida con Cuenca).</t>
+  </si>
+  <si>
+    <t>INGEVIA interno: terreno en venta, Enchilagar, Vilamarxant (Idealista, 2.929 m², 80.000€). Catastral, estudio de implantación. @ingevia.com, M. Vera.</t>
+  </si>
+  <si>
+    <t>INGEVIA interno: posible estación MIDES, Manises, Avda Mas de l'Oli 190. Crear carpeta, planta de implantación con lavadero. @ingevia.com, M. Vera.</t>
+  </si>
+  <si>
+    <t>INGEVIA interno: posible MIDES, Manises, Avda Mas de l'Oli 17 (polígono industrial; distinta de la parcela del nº190). Imágenes de ubicación. @ingevia.com, M. Vera.</t>
+  </si>
+  <si>
+    <t>INGEVIA interno: parcela/nave, Manises, C/ Santos Justo y Pastor (polígono aeropuerto, junto aeropuerto Valencia-Manises). Imágenes de ubicación. @ingevia.com, M. Vera.</t>
+  </si>
+  <si>
+    <t>INGEVIA interno: parcela en Camí Llíria-Magraners, Puçol. Estudio de implantación + plano catastral (PDF/DWG), salida sin correo de origen. @ingevia.com, M. Vera.</t>
+  </si>
+  <si>
+    <t>INGEVIA interno: parcela en Ronda Nord, Catarroja. Solo archivo CAD (DWG) del estudio de implantación, salida sin correo de origen. @ingevia.com, M. Vera.</t>
+  </si>
+  <si>
+    <t>INGEVIA interno: nave industrial en venta, Cuenca (Idealista, 430.000€, 850/700 m², 2 baños). Crear carpeta, descargar info. @ingevia.com, M. Vera.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -1435,12 +1441,6 @@
       <sz val="11"/>
       <color indexed="8"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1550,7 +1550,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1571,9 +1571,6 @@
     <xf numFmtId="49" fontId="4" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1589,16 +1586,26 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="8" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2767,11 +2774,11 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:4" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
     </row>
     <row r="7" spans="2:4" ht="18.5" x14ac:dyDescent="0.45">
       <c r="B7" s="1" t="s">
@@ -2837,7 +2844,7 @@
     <col min="2" max="2" width="32" style="5" customWidth="1"/>
     <col min="3" max="3" width="70.54296875" style="5" customWidth="1"/>
     <col min="4" max="4" width="8" style="5" customWidth="1"/>
-    <col min="5" max="6" width="81.453125" style="5" customWidth="1"/>
+    <col min="5" max="6" width="81.453125" style="23" customWidth="1"/>
     <col min="7" max="7" width="8.81640625" style="5" customWidth="1"/>
     <col min="8" max="16384" width="8.81640625" style="5"/>
   </cols>
@@ -2855,1169 +2862,1173 @@
       <c r="D1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="E1" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="24" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="10">
+      <c r="D2" s="9">
         <v>2026</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="20" t="s">
+        <v>397</v>
+      </c>
+      <c r="F2" s="21" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="11">
+        <v>2026</v>
+      </c>
+      <c r="E3" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="11">
+        <v>2026</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>399</v>
+      </c>
+      <c r="F4" s="21" t="s">
         <v>424</v>
       </c>
-      <c r="F2" t="s">
+    </row>
+    <row r="5" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="11">
+        <v>2026</v>
+      </c>
+      <c r="E5" s="21" t="s">
+        <v>399</v>
+      </c>
+      <c r="F5" s="21" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="11" t="s">
+    <row r="6" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" s="12">
+      <c r="C6" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="11">
         <v>2026</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E6" s="21" t="s">
+        <v>399</v>
+      </c>
+      <c r="F6" s="21" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="11">
+        <v>2026</v>
+      </c>
+      <c r="E7" s="21" t="s">
+        <v>399</v>
+      </c>
+      <c r="F7" s="21" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="11">
+        <v>2026</v>
+      </c>
+      <c r="E8" s="21" t="s">
+        <v>399</v>
+      </c>
+      <c r="F8" s="21" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="11">
+        <v>2026</v>
+      </c>
+      <c r="E9" s="21" t="s">
+        <v>399</v>
+      </c>
+      <c r="F9" s="21" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" s="11">
+        <v>2026</v>
+      </c>
+      <c r="E10" s="20" t="s">
+        <v>400</v>
+      </c>
+      <c r="F10" s="21" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" s="11">
+        <v>2026</v>
+      </c>
+      <c r="E11" s="20" t="s">
+        <v>400</v>
+      </c>
+      <c r="F11" s="21" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D12" s="11">
+        <v>2026</v>
+      </c>
+      <c r="E12" s="20" t="s">
+        <v>400</v>
+      </c>
+      <c r="F12" s="21" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" s="11">
+        <v>2026</v>
+      </c>
+      <c r="E13" s="20" t="s">
+        <v>400</v>
+      </c>
+      <c r="F13" s="21" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" s="11">
+        <v>2026</v>
+      </c>
+      <c r="E14" s="20" t="s">
+        <v>400</v>
+      </c>
+      <c r="F14" s="21" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="D15" s="11">
+        <v>2026</v>
+      </c>
+      <c r="E15" s="20" t="s">
+        <v>400</v>
+      </c>
+      <c r="F15" s="18" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D16" s="11">
+        <v>2026</v>
+      </c>
+      <c r="E16" s="20" t="s">
+        <v>400</v>
+      </c>
+      <c r="F16" s="22" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D17" s="11">
+        <v>2026</v>
+      </c>
+      <c r="E17" s="20" t="s">
+        <v>400</v>
+      </c>
+      <c r="F17" s="21" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="D18" s="11">
+        <v>2026</v>
+      </c>
+      <c r="E18" s="20" t="s">
+        <v>400</v>
+      </c>
+      <c r="F18" s="21" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="D19" s="11">
+        <v>2026</v>
+      </c>
+      <c r="E19" s="21" t="s">
+        <v>401</v>
+      </c>
+      <c r="F19" s="21" t="s">
+        <v>438</v>
+      </c>
+      <c r="G19" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="D20" s="11">
+        <v>2026</v>
+      </c>
+      <c r="E20" s="21" t="s">
+        <v>401</v>
+      </c>
+      <c r="F20" s="21" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="D21" s="11">
+        <v>2026</v>
+      </c>
+      <c r="E21" s="21" t="s">
+        <v>401</v>
+      </c>
+      <c r="F21" s="21" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="D22" s="11">
+        <v>2026</v>
+      </c>
+      <c r="E22" s="21" t="s">
+        <v>401</v>
+      </c>
+      <c r="F22" s="21" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="D23" s="11">
+        <v>2026</v>
+      </c>
+      <c r="E23" s="21" t="s">
+        <v>401</v>
+      </c>
+      <c r="F23" s="21" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="D24" s="11">
+        <v>2026</v>
+      </c>
+      <c r="E24" s="21" t="s">
+        <v>401</v>
+      </c>
+      <c r="F24" s="21" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="D25" s="11">
+        <v>2026</v>
+      </c>
+      <c r="E25" s="21" t="s">
+        <v>401</v>
+      </c>
+      <c r="F25" s="21" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="D26" s="11">
+        <v>2026</v>
+      </c>
+      <c r="E26" s="21" t="s">
+        <v>401</v>
+      </c>
+      <c r="F26" s="21" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="D27" s="11">
+        <v>2026</v>
+      </c>
+      <c r="E27" s="21" t="s">
+        <v>401</v>
+      </c>
+      <c r="F27" s="21" t="s">
         <v>446</v>
       </c>
-      <c r="F3" t="s">
+    </row>
+    <row r="28" spans="1:7" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="D28" s="11">
+        <v>2026</v>
+      </c>
+      <c r="E28" s="21" t="s">
+        <v>401</v>
+      </c>
+      <c r="F28" s="21" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="12">
+    <row r="29" spans="1:7" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="B29" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="D29" s="11">
         <v>2026</v>
       </c>
-      <c r="E4" t="s">
-        <v>446</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="E29" s="20" t="s">
+        <v>402</v>
+      </c>
+      <c r="F29" s="22" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>389</v>
+      </c>
+      <c r="D30" s="11">
+        <v>2026</v>
+      </c>
+      <c r="E30" s="20" t="s">
+        <v>407</v>
+      </c>
+      <c r="F30" s="21" t="s">
         <v>448</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="12">
+    <row r="31" spans="1:7" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="B31" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="C31" s="12" t="s">
+        <v>390</v>
+      </c>
+      <c r="D31" s="11">
         <v>2026</v>
       </c>
-      <c r="E5" t="s">
-        <v>446</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="E31" s="20" t="s">
+        <v>407</v>
+      </c>
+      <c r="F31" s="21" t="s">
         <v>449</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" s="12">
+    <row r="32" spans="1:7" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="C32" s="12" t="s">
+        <v>391</v>
+      </c>
+      <c r="D32" s="11">
         <v>2026</v>
       </c>
-      <c r="E6" t="s">
-        <v>446</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="E32" s="20" t="s">
+        <v>407</v>
+      </c>
+      <c r="F32" s="21" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="12">
+    <row r="33" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="B33" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="C33" s="12" t="s">
+        <v>392</v>
+      </c>
+      <c r="D33" s="11">
         <v>2026</v>
       </c>
-      <c r="E7" t="s">
-        <v>446</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="E33" s="20" t="s">
+        <v>407</v>
+      </c>
+      <c r="F33" s="21" t="s">
         <v>451</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" s="12">
+    <row r="34" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>393</v>
+      </c>
+      <c r="D34" s="11">
         <v>2026</v>
       </c>
-      <c r="E8" t="s">
-        <v>446</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="E34" s="20" t="s">
+        <v>407</v>
+      </c>
+      <c r="F34" s="21" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" s="12">
+    <row r="35" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="B35" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>394</v>
+      </c>
+      <c r="D35" s="11">
         <v>2026</v>
       </c>
-      <c r="E9" t="s">
-        <v>446</v>
-      </c>
-      <c r="F9" t="s">
+      <c r="E35" s="20" t="s">
+        <v>407</v>
+      </c>
+      <c r="F35" s="21" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="D10" s="12">
+    <row r="36" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="B36" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="C36" s="12" t="s">
+        <v>395</v>
+      </c>
+      <c r="D36" s="11">
         <v>2026</v>
       </c>
-      <c r="E10" t="s">
-        <v>437</v>
-      </c>
-      <c r="F10" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="D11" s="12">
+      <c r="E36" s="20" t="s">
+        <v>407</v>
+      </c>
+      <c r="F36" s="21" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="B37" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D37" s="11">
         <v>2026</v>
       </c>
-      <c r="E11" t="s">
-        <v>437</v>
-      </c>
-      <c r="F11" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="D12" s="12">
+      <c r="E37" s="21" t="s">
+        <v>406</v>
+      </c>
+      <c r="F37" s="22" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="C38" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="D38" s="11">
         <v>2026</v>
       </c>
-      <c r="E12" t="s">
-        <v>437</v>
-      </c>
-      <c r="F12" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="D13" s="12">
+      <c r="E38" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="F38" s="25" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A39" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="C39" s="12" t="s">
+        <v>388</v>
+      </c>
+      <c r="D39" s="11">
         <v>2026</v>
       </c>
-      <c r="E13" t="s">
-        <v>437</v>
-      </c>
-      <c r="F13" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="D14" s="12">
+      <c r="E39" s="22" t="s">
+        <v>388</v>
+      </c>
+      <c r="F39" s="22" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="B40" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="C40" s="12" t="s">
+        <v>388</v>
+      </c>
+      <c r="D40" s="11">
         <v>2026</v>
       </c>
-      <c r="E14" t="s">
-        <v>437</v>
-      </c>
-      <c r="F14" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="D15" s="12">
+      <c r="E40" s="22" t="s">
+        <v>388</v>
+      </c>
+      <c r="F40" s="22" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="B41" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="C41" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="D41" s="11">
         <v>2026</v>
       </c>
-      <c r="E15" t="s">
-        <v>437</v>
-      </c>
-      <c r="F15" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="D16" s="12">
+      <c r="E41" s="21" t="s">
+        <v>405</v>
+      </c>
+      <c r="F41" s="22" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="B42" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="C42" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="D42" s="11">
         <v>2026</v>
       </c>
-      <c r="E16" t="s">
-        <v>437</v>
-      </c>
-      <c r="F16" s="13" t="s">
+      <c r="E42" s="22" t="s">
         <v>388</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="D17" s="12">
+      <c r="F42" s="22" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="C43" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="D43" s="11">
         <v>2026</v>
       </c>
-      <c r="E17" t="s">
-        <v>437</v>
-      </c>
-      <c r="F17" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="D18" s="12">
+      <c r="E43" s="21" t="s">
+        <v>404</v>
+      </c>
+      <c r="F43" s="22" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="B44" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="C44" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="D44" s="11">
         <v>2026</v>
       </c>
-      <c r="E18" t="s">
-        <v>437</v>
-      </c>
-      <c r="F18" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="B19" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="D19" s="12">
+      <c r="E44" s="21" t="s">
+        <v>404</v>
+      </c>
+      <c r="F44" s="22" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C45" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="D45" s="11">
         <v>2026</v>
       </c>
-      <c r="E19" t="s">
-        <v>426</v>
-      </c>
-      <c r="F19" t="s">
-        <v>427</v>
-      </c>
-      <c r="G19" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="D20" s="12">
+      <c r="E45" s="22" t="s">
+        <v>388</v>
+      </c>
+      <c r="F45" s="22" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="B46" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="C46" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="D46" s="11">
         <v>2026</v>
       </c>
-      <c r="E20" t="s">
-        <v>426</v>
-      </c>
-      <c r="F20" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="B21" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="C21" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="D21" s="12">
+      <c r="E46" s="21" t="s">
+        <v>403</v>
+      </c>
+      <c r="F46" s="22" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="B47" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="C47" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D47" s="11">
         <v>2026</v>
       </c>
-      <c r="E21" t="s">
-        <v>426</v>
-      </c>
-      <c r="F21" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="B22" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="D22" s="12">
+      <c r="E47" s="21" t="s">
+        <v>409</v>
+      </c>
+      <c r="F47" s="22" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="B48" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="C48" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="D48" s="11">
         <v>2026</v>
       </c>
-      <c r="E22" t="s">
-        <v>426</v>
-      </c>
-      <c r="F22" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="B23" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="D23" s="12">
+      <c r="E48" s="20" t="s">
+        <v>410</v>
+      </c>
+      <c r="F48" s="22" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="B49" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="C49" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="D49" s="11">
         <v>2026</v>
       </c>
-      <c r="E23" t="s">
-        <v>426</v>
-      </c>
-      <c r="F23" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="B24" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="C24" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="D24" s="12">
+      <c r="E49" s="20" t="s">
+        <v>411</v>
+      </c>
+      <c r="F49" s="22" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="B50" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="C50" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D50" s="11">
         <v>2026</v>
       </c>
-      <c r="E24" t="s">
-        <v>426</v>
-      </c>
-      <c r="F24" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="B25" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="D25" s="12">
+      <c r="E50" s="21" t="s">
+        <v>412</v>
+      </c>
+      <c r="F50" s="22" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="B51" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="C51" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="D51" s="11">
         <v>2026</v>
       </c>
-      <c r="E25" t="s">
-        <v>426</v>
-      </c>
-      <c r="F25" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="B26" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="C26" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="D26" s="12">
+      <c r="E51" s="21" t="s">
+        <v>413</v>
+      </c>
+      <c r="F51" s="22" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="B52" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="C52" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="D52" s="11">
         <v>2026</v>
       </c>
-      <c r="E26" t="s">
-        <v>426</v>
-      </c>
-      <c r="F26" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="B27" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="C27" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="D27" s="12">
+      <c r="E52" s="21" t="s">
+        <v>414</v>
+      </c>
+      <c r="F52" s="26" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="B53" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="C53" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="D53" s="11">
         <v>2026</v>
       </c>
-      <c r="E27" t="s">
-        <v>426</v>
-      </c>
-      <c r="F27" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="B28" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="C28" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="D28" s="12">
+      <c r="E53" s="21" t="s">
+        <v>415</v>
+      </c>
+      <c r="F53" s="22" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="B54" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="C54" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="D54" s="11">
         <v>2026</v>
       </c>
-      <c r="E28" t="s">
-        <v>426</v>
-      </c>
-      <c r="F28" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="B29" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="C29" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="D29" s="12">
+      <c r="E54" s="21" t="s">
+        <v>416</v>
+      </c>
+      <c r="F54" s="22" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="B55" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="C55" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="D55" s="11">
         <v>2026</v>
       </c>
-      <c r="E29" t="s">
-        <v>423</v>
-      </c>
-      <c r="F29" s="13" t="s">
+      <c r="E55" s="21" t="s">
+        <v>417</v>
+      </c>
+      <c r="F55" s="22" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="B30" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="C30" s="13" t="s">
-        <v>408</v>
-      </c>
-      <c r="D30" s="12">
+    <row r="56" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="B56" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="C56" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="D56" s="11">
         <v>2026</v>
       </c>
-      <c r="E30" t="s">
-        <v>415</v>
-      </c>
-      <c r="F30" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="B31" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="C31" s="13" t="s">
-        <v>409</v>
-      </c>
-      <c r="D31" s="12">
+      <c r="E56" s="21" t="s">
+        <v>418</v>
+      </c>
+      <c r="F56" s="22" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="B57" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="C57" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="D57" s="11">
         <v>2026</v>
       </c>
-      <c r="E31" t="s">
-        <v>415</v>
-      </c>
-      <c r="F31" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="B32" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="C32" s="13" t="s">
-        <v>410</v>
-      </c>
-      <c r="D32" s="12">
+      <c r="E57" s="21" t="s">
+        <v>419</v>
+      </c>
+      <c r="F57" s="22" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="B58" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="C58" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="D58" s="11">
         <v>2026</v>
       </c>
-      <c r="E32" t="s">
-        <v>415</v>
-      </c>
-      <c r="F32" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="B33" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="C33" s="13" t="s">
-        <v>411</v>
-      </c>
-      <c r="D33" s="12">
+      <c r="E58" s="21" t="s">
+        <v>420</v>
+      </c>
+      <c r="F58" s="22" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="B59" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="C59" s="12" t="s">
+        <v>388</v>
+      </c>
+      <c r="D59" s="11">
         <v>2026</v>
       </c>
-      <c r="E33" t="s">
-        <v>415</v>
-      </c>
-      <c r="F33" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="B34" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="C34" s="13" t="s">
-        <v>412</v>
-      </c>
-      <c r="D34" s="12">
-        <v>2026</v>
-      </c>
-      <c r="E34" t="s">
-        <v>415</v>
-      </c>
-      <c r="F34" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="B35" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="C35" s="13" t="s">
-        <v>413</v>
-      </c>
-      <c r="D35" s="12">
-        <v>2026</v>
-      </c>
-      <c r="E35" t="s">
-        <v>415</v>
-      </c>
-      <c r="F35" t="s">
+      <c r="E59" s="21" t="s">
         <v>421</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="B36" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="C36" s="13" t="s">
-        <v>414</v>
-      </c>
-      <c r="D36" s="12">
-        <v>2026</v>
-      </c>
-      <c r="E36" t="s">
-        <v>415</v>
-      </c>
-      <c r="F36" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="B37" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="C37" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="D37" s="12">
-        <v>2026</v>
-      </c>
-      <c r="E37" t="s">
-        <v>407</v>
-      </c>
-      <c r="F37" s="13"/>
-    </row>
-    <row r="38" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="B38" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="C38" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="D38" s="12">
-        <v>2026</v>
-      </c>
-      <c r="E38" t="s">
-        <v>406</v>
-      </c>
-      <c r="F38" s="13"/>
-    </row>
-    <row r="39" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="B39" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="C39" s="13" t="s">
-        <v>388</v>
-      </c>
-      <c r="D39" s="12">
-        <v>2026</v>
-      </c>
-      <c r="E39" s="13" t="s">
-        <v>388</v>
-      </c>
-      <c r="F39" s="13" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="B40" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="C40" s="13" t="s">
-        <v>388</v>
-      </c>
-      <c r="D40" s="12">
-        <v>2026</v>
-      </c>
-      <c r="E40" s="13" t="s">
-        <v>388</v>
-      </c>
-      <c r="F40" s="13" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="B41" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="C41" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="D41" s="12">
-        <v>2026</v>
-      </c>
-      <c r="E41" t="s">
-        <v>405</v>
-      </c>
-      <c r="F41" s="13" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="B42" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="C42" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="D42" s="12">
-        <v>2026</v>
-      </c>
-      <c r="E42" s="13" t="s">
-        <v>388</v>
-      </c>
-      <c r="F42" s="13" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="B43" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="C43" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="D43" s="12">
-        <v>2026</v>
-      </c>
-      <c r="E43" t="s">
-        <v>404</v>
-      </c>
-      <c r="F43" s="13" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="B44" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="C44" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="D44" s="12">
-        <v>2026</v>
-      </c>
-      <c r="E44" t="s">
-        <v>403</v>
-      </c>
-      <c r="F44" s="13" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="B45" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C45" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="D45" s="12">
-        <v>2026</v>
-      </c>
-      <c r="E45" s="13" t="s">
-        <v>388</v>
-      </c>
-      <c r="F45" s="13" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="B46" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="C46" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="D46" s="12">
-        <v>2026</v>
-      </c>
-      <c r="E46" t="s">
-        <v>402</v>
-      </c>
-      <c r="F46" s="13" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="B47" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="C47" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="D47" s="12">
-        <v>2026</v>
-      </c>
-      <c r="E47" t="s">
-        <v>401</v>
-      </c>
-      <c r="F47" s="13" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="B48" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="C48" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="D48" s="12">
-        <v>2026</v>
-      </c>
-      <c r="E48" t="s">
-        <v>400</v>
-      </c>
-      <c r="F48" s="13" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="B49" s="11" t="s">
-        <v>105</v>
-      </c>
-      <c r="C49" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="D49" s="12">
-        <v>2026</v>
-      </c>
-      <c r="E49" t="s">
-        <v>399</v>
-      </c>
-      <c r="F49" s="13" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="11" t="s">
-        <v>107</v>
-      </c>
-      <c r="B50" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="C50" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="D50" s="12">
-        <v>2026</v>
-      </c>
-      <c r="E50" t="s">
-        <v>398</v>
-      </c>
-      <c r="F50" s="13" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="B51" s="19" t="s">
-        <v>111</v>
-      </c>
-      <c r="C51" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="D51" s="12">
-        <v>2026</v>
-      </c>
-      <c r="E51" t="s">
-        <v>397</v>
-      </c>
-      <c r="F51" s="13" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="B52" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="C52" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="D52" s="12">
-        <v>2026</v>
-      </c>
-      <c r="E52" s="16" t="s">
-        <v>396</v>
-      </c>
-      <c r="F52" s="17" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="B53" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="C53" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="D53" s="12">
-        <v>2026</v>
-      </c>
-      <c r="E53" t="s">
-        <v>395</v>
-      </c>
-      <c r="F53" s="13" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="B54" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="C54" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="D54" s="12">
-        <v>2026</v>
-      </c>
-      <c r="E54" t="s">
-        <v>394</v>
-      </c>
-      <c r="F54" s="13" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="B55" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="C55" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="D55" s="12">
-        <v>2026</v>
-      </c>
-      <c r="E55" t="s">
-        <v>393</v>
-      </c>
-      <c r="F55" s="13" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="B56" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="C56" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="D56" s="12">
-        <v>2026</v>
-      </c>
-      <c r="E56" s="13" t="s">
-        <v>392</v>
-      </c>
-      <c r="F56" s="13" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="B57" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="C57" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="D57" s="12">
-        <v>2026</v>
-      </c>
-      <c r="E57" s="13" t="s">
-        <v>391</v>
-      </c>
-      <c r="F57" s="13" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="B58" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="C58" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="D58" s="12">
-        <v>2026</v>
-      </c>
-      <c r="E58" s="13" t="s">
-        <v>390</v>
-      </c>
-      <c r="F58" s="13" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="B59" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="C59" s="13" t="s">
-        <v>388</v>
-      </c>
-      <c r="D59" s="12">
-        <v>2026</v>
-      </c>
-      <c r="E59" s="13" t="s">
-        <v>389</v>
-      </c>
-      <c r="F59" s="13" t="s">
+      <c r="F59" s="22" t="s">
         <v>388</v>
       </c>
     </row>
@@ -4066,1770 +4077,1770 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="D2" s="10">
-        <v>2025</v>
-      </c>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
+      <c r="D2" s="9">
+        <v>2025</v>
+      </c>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
     </row>
     <row r="3" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="D3" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
+      <c r="D3" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
     </row>
     <row r="4" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="D4" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
+      <c r="D4" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
     </row>
     <row r="5" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="D5" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E5" s="15"/>
-      <c r="F5" s="15"/>
+      <c r="D5" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
     </row>
     <row r="6" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="D6" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
+      <c r="D6" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14"/>
     </row>
     <row r="7" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="D7" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
+      <c r="D7" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
     </row>
     <row r="8" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="D8" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
+      <c r="D8" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
     </row>
     <row r="9" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="D9" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
+      <c r="D9" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14"/>
     </row>
     <row r="10" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="D10" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
+      <c r="D10" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
     </row>
     <row r="11" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="D11" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
+      <c r="D11" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
     </row>
     <row r="12" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="D12" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
+      <c r="D12" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
     </row>
     <row r="13" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="D13" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
+      <c r="D13" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
     </row>
     <row r="14" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="D14" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
+      <c r="D14" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
     </row>
     <row r="15" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="D15" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
+      <c r="D15" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
     </row>
     <row r="16" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="11" t="s">
+      <c r="A16" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="D16" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
+      <c r="D16" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
     </row>
     <row r="17" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="11" t="s">
+      <c r="A17" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C17" s="10" t="s">
         <v>171</v>
       </c>
-      <c r="D17" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
+      <c r="D17" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
     </row>
     <row r="18" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C18" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="D18" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
+      <c r="D18" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
     </row>
     <row r="19" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="11" t="s">
+      <c r="A19" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="B19" s="11" t="s">
+      <c r="B19" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="C19" s="11" t="s">
+      <c r="C19" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="D19" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
+      <c r="D19" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E19" s="14"/>
+      <c r="F19" s="14"/>
     </row>
     <row r="20" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="11" t="s">
+      <c r="A20" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="B20" s="11" t="s">
+      <c r="B20" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="C20" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="D20" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
+      <c r="D20" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E20" s="14"/>
+      <c r="F20" s="14"/>
     </row>
     <row r="21" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="11" t="s">
+      <c r="A21" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="B21" s="11" t="s">
+      <c r="B21" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="C21" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="D21" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
+      <c r="D21" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
     </row>
     <row r="22" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="11" t="s">
+      <c r="A22" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="B22" s="11" t="s">
+      <c r="B22" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="C22" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="D22" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
+      <c r="D22" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E22" s="14"/>
+      <c r="F22" s="14"/>
     </row>
     <row r="23" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="11" t="s">
+      <c r="A23" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="B23" s="11" t="s">
+      <c r="B23" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="C23" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="D23" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
+      <c r="D23" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E23" s="14"/>
+      <c r="F23" s="14"/>
     </row>
     <row r="24" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="11" t="s">
+      <c r="A24" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="B24" s="11" t="s">
+      <c r="B24" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="C24" s="11" t="s">
+      <c r="C24" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="D24" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E24" s="15"/>
-      <c r="F24" s="15"/>
+      <c r="D24" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
     </row>
     <row r="25" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="11" t="s">
+      <c r="A25" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="B25" s="11" t="s">
+      <c r="B25" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="C25" s="11" t="s">
+      <c r="C25" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="D25" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E25" s="15"/>
-      <c r="F25" s="15"/>
+      <c r="D25" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E25" s="14"/>
+      <c r="F25" s="14"/>
     </row>
     <row r="26" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="11" t="s">
+      <c r="A26" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="B26" s="11" t="s">
+      <c r="B26" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="C26" s="11" t="s">
+      <c r="C26" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="D26" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E26" s="15"/>
-      <c r="F26" s="15"/>
+      <c r="D26" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E26" s="14"/>
+      <c r="F26" s="14"/>
     </row>
     <row r="27" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="11" t="s">
+      <c r="A27" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="B27" s="11" t="s">
+      <c r="B27" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="C27" s="11" t="s">
+      <c r="C27" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="D27" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E27" s="15"/>
-      <c r="F27" s="15"/>
+      <c r="D27" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E27" s="14"/>
+      <c r="F27" s="14"/>
     </row>
     <row r="28" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="11" t="s">
+      <c r="A28" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="B28" s="11" t="s">
+      <c r="B28" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="C28" s="11" t="s">
+      <c r="C28" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="D28" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E28" s="15"/>
-      <c r="F28" s="15"/>
+      <c r="D28" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E28" s="14"/>
+      <c r="F28" s="14"/>
     </row>
     <row r="29" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="11" t="s">
+      <c r="A29" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="B29" s="11" t="s">
+      <c r="B29" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="C29" s="11" t="s">
+      <c r="C29" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="D29" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E29" s="15"/>
-      <c r="F29" s="15"/>
+      <c r="D29" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E29" s="14"/>
+      <c r="F29" s="14"/>
     </row>
     <row r="30" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="11" t="s">
+      <c r="A30" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="B30" s="11" t="s">
+      <c r="B30" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="C30" s="11" t="s">
+      <c r="C30" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="D30" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E30" s="15"/>
-      <c r="F30" s="15"/>
+      <c r="D30" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
     </row>
     <row r="31" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="11" t="s">
+      <c r="A31" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="B31" s="11" t="s">
+      <c r="B31" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="C31" s="11" t="s">
+      <c r="C31" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="D31" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E31" s="15"/>
-      <c r="F31" s="15"/>
+      <c r="D31" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
     </row>
     <row r="32" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="11" t="s">
+      <c r="A32" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="B32" s="11" t="s">
+      <c r="B32" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="C32" s="11" t="s">
+      <c r="C32" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="D32" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E32" s="15"/>
-      <c r="F32" s="15"/>
+      <c r="D32" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E32" s="14"/>
+      <c r="F32" s="14"/>
     </row>
     <row r="33" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="11" t="s">
+      <c r="A33" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="B33" s="11" t="s">
+      <c r="B33" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="C33" s="11" t="s">
+      <c r="C33" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="D33" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E33" s="15"/>
-      <c r="F33" s="15"/>
+      <c r="D33" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E33" s="14"/>
+      <c r="F33" s="14"/>
     </row>
     <row r="34" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="11" t="s">
+      <c r="A34" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="B34" s="11" t="s">
+      <c r="B34" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="C34" s="11" t="s">
+      <c r="C34" s="10" t="s">
         <v>205</v>
       </c>
-      <c r="D34" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E34" s="15"/>
-      <c r="F34" s="15"/>
+      <c r="D34" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E34" s="14"/>
+      <c r="F34" s="14"/>
     </row>
     <row r="35" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="11" t="s">
+      <c r="A35" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="B35" s="11" t="s">
+      <c r="B35" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="C35" s="11" t="s">
+      <c r="C35" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="D35" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E35" s="15"/>
-      <c r="F35" s="15"/>
+      <c r="D35" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E35" s="14"/>
+      <c r="F35" s="14"/>
     </row>
     <row r="36" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="11" t="s">
+      <c r="A36" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="B36" s="11" t="s">
+      <c r="B36" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="C36" s="11" t="s">
+      <c r="C36" s="10" t="s">
         <v>209</v>
       </c>
-      <c r="D36" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E36" s="15"/>
-      <c r="F36" s="15"/>
+      <c r="D36" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E36" s="14"/>
+      <c r="F36" s="14"/>
     </row>
     <row r="37" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="11" t="s">
+      <c r="A37" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="B37" s="11" t="s">
+      <c r="B37" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="C37" s="11" t="s">
+      <c r="C37" s="10" t="s">
         <v>211</v>
       </c>
-      <c r="D37" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E37" s="15"/>
-      <c r="F37" s="15"/>
+      <c r="D37" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E37" s="14"/>
+      <c r="F37" s="14"/>
     </row>
     <row r="38" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="11" t="s">
+      <c r="A38" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="B38" s="11" t="s">
+      <c r="B38" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="C38" s="11" t="s">
+      <c r="C38" s="10" t="s">
         <v>213</v>
       </c>
-      <c r="D38" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E38" s="15"/>
-      <c r="F38" s="15"/>
+      <c r="D38" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E38" s="14"/>
+      <c r="F38" s="14"/>
     </row>
     <row r="39" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="11" t="s">
+      <c r="A39" s="10" t="s">
         <v>214</v>
       </c>
-      <c r="B39" s="11" t="s">
+      <c r="B39" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="C39" s="11" t="s">
+      <c r="C39" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="D39" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E39" s="15"/>
-      <c r="F39" s="15"/>
+      <c r="D39" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E39" s="14"/>
+      <c r="F39" s="14"/>
     </row>
     <row r="40" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="11" t="s">
+      <c r="A40" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="B40" s="11" t="s">
+      <c r="B40" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="C40" s="11" t="s">
+      <c r="C40" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="D40" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E40" s="15"/>
-      <c r="F40" s="15"/>
+      <c r="D40" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E40" s="14"/>
+      <c r="F40" s="14"/>
     </row>
     <row r="41" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="11" t="s">
+      <c r="A41" s="10" t="s">
         <v>216</v>
       </c>
-      <c r="B41" s="11" t="s">
+      <c r="B41" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="C41" s="11" t="s">
+      <c r="C41" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="D41" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E41" s="15"/>
-      <c r="F41" s="15"/>
+      <c r="D41" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E41" s="14"/>
+      <c r="F41" s="14"/>
     </row>
     <row r="42" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="11" t="s">
+      <c r="A42" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="B42" s="11" t="s">
+      <c r="B42" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="C42" s="11" t="s">
+      <c r="C42" s="10" t="s">
         <v>219</v>
       </c>
-      <c r="D42" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E42" s="15"/>
-      <c r="F42" s="15"/>
+      <c r="D42" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E42" s="14"/>
+      <c r="F42" s="14"/>
     </row>
     <row r="43" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="11" t="s">
+      <c r="A43" s="10" t="s">
         <v>220</v>
       </c>
-      <c r="B43" s="11" t="s">
+      <c r="B43" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="C43" s="11" t="s">
+      <c r="C43" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="D43" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E43" s="15"/>
-      <c r="F43" s="15"/>
+      <c r="D43" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E43" s="14"/>
+      <c r="F43" s="14"/>
     </row>
     <row r="44" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="11" t="s">
+      <c r="A44" s="10" t="s">
         <v>221</v>
       </c>
-      <c r="B44" s="11" t="s">
+      <c r="B44" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="C44" s="11" t="s">
+      <c r="C44" s="10" t="s">
         <v>222</v>
       </c>
-      <c r="D44" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E44" s="15"/>
-      <c r="F44" s="15"/>
+      <c r="D44" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E44" s="14"/>
+      <c r="F44" s="14"/>
     </row>
     <row r="45" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="11" t="s">
+      <c r="A45" s="10" t="s">
         <v>223</v>
       </c>
-      <c r="B45" s="11" t="s">
+      <c r="B45" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="C45" s="11" t="s">
+      <c r="C45" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="D45" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E45" s="15"/>
-      <c r="F45" s="15"/>
+      <c r="D45" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E45" s="14"/>
+      <c r="F45" s="14"/>
     </row>
     <row r="46" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="11" t="s">
+      <c r="A46" s="10" t="s">
         <v>224</v>
       </c>
-      <c r="B46" s="11" t="s">
+      <c r="B46" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="C46" s="11" t="s">
+      <c r="C46" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="D46" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E46" s="15"/>
-      <c r="F46" s="15"/>
+      <c r="D46" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E46" s="14"/>
+      <c r="F46" s="14"/>
     </row>
     <row r="47" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="11" t="s">
+      <c r="A47" s="10" t="s">
         <v>226</v>
       </c>
-      <c r="B47" s="11" t="s">
+      <c r="B47" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="C47" s="11" t="s">
+      <c r="C47" s="10" t="s">
         <v>227</v>
       </c>
-      <c r="D47" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E47" s="15"/>
-      <c r="F47" s="15"/>
+      <c r="D47" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E47" s="14"/>
+      <c r="F47" s="14"/>
     </row>
     <row r="48" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="11" t="s">
+      <c r="A48" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="B48" s="11" t="s">
+      <c r="B48" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="C48" s="11" t="s">
+      <c r="C48" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="D48" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E48" s="15"/>
-      <c r="F48" s="15"/>
+      <c r="D48" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E48" s="14"/>
+      <c r="F48" s="14"/>
     </row>
     <row r="49" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="11" t="s">
+      <c r="A49" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="B49" s="11" t="s">
+      <c r="B49" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C49" s="11" t="s">
+      <c r="C49" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="D49" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E49" s="15"/>
-      <c r="F49" s="15"/>
+      <c r="D49" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E49" s="14"/>
+      <c r="F49" s="14"/>
     </row>
     <row r="50" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="11" t="s">
+      <c r="A50" s="10" t="s">
         <v>232</v>
       </c>
-      <c r="B50" s="11" t="s">
+      <c r="B50" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C50" s="11" t="s">
+      <c r="C50" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="D50" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E50" s="15"/>
-      <c r="F50" s="15"/>
+      <c r="D50" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E50" s="14"/>
+      <c r="F50" s="14"/>
     </row>
     <row r="51" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="11" t="s">
+      <c r="A51" s="10" t="s">
         <v>234</v>
       </c>
-      <c r="B51" s="11" t="s">
+      <c r="B51" s="10" t="s">
         <v>235</v>
       </c>
-      <c r="C51" s="11" t="s">
+      <c r="C51" s="10" t="s">
         <v>236</v>
       </c>
-      <c r="D51" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E51" s="15"/>
-      <c r="F51" s="15"/>
+      <c r="D51" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E51" s="14"/>
+      <c r="F51" s="14"/>
     </row>
     <row r="52" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="11" t="s">
+      <c r="A52" s="10" t="s">
         <v>237</v>
       </c>
-      <c r="B52" s="11" t="s">
+      <c r="B52" s="10" t="s">
         <v>238</v>
       </c>
-      <c r="C52" s="11" t="s">
+      <c r="C52" s="10" t="s">
         <v>239</v>
       </c>
-      <c r="D52" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E52" s="15"/>
-      <c r="F52" s="15"/>
+      <c r="D52" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E52" s="14"/>
+      <c r="F52" s="14"/>
     </row>
     <row r="53" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="11" t="s">
+      <c r="A53" s="10" t="s">
         <v>240</v>
       </c>
-      <c r="B53" s="11" t="s">
+      <c r="B53" s="10" t="s">
         <v>241</v>
       </c>
-      <c r="C53" s="11" t="s">
+      <c r="C53" s="10" t="s">
         <v>242</v>
       </c>
-      <c r="D53" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E53" s="15"/>
-      <c r="F53" s="15"/>
+      <c r="D53" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E53" s="14"/>
+      <c r="F53" s="14"/>
     </row>
     <row r="54" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="11" t="s">
+      <c r="A54" s="10" t="s">
         <v>243</v>
       </c>
-      <c r="B54" s="11" t="s">
+      <c r="B54" s="10" t="s">
         <v>244</v>
       </c>
-      <c r="C54" s="13"/>
-      <c r="D54" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E54" s="15"/>
-      <c r="F54" s="15"/>
+      <c r="C54" s="12"/>
+      <c r="D54" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E54" s="14"/>
+      <c r="F54" s="14"/>
     </row>
     <row r="55" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="11" t="s">
+      <c r="A55" s="10" t="s">
         <v>245</v>
       </c>
-      <c r="B55" s="11" t="s">
+      <c r="B55" s="10" t="s">
         <v>246</v>
       </c>
-      <c r="C55" s="11" t="s">
+      <c r="C55" s="10" t="s">
         <v>247</v>
       </c>
-      <c r="D55" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E55" s="15"/>
-      <c r="F55" s="15"/>
+      <c r="D55" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E55" s="14"/>
+      <c r="F55" s="14"/>
     </row>
     <row r="56" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="11" t="s">
+      <c r="A56" s="10" t="s">
         <v>248</v>
       </c>
-      <c r="B56" s="11" t="s">
+      <c r="B56" s="10" t="s">
         <v>249</v>
       </c>
-      <c r="C56" s="11" t="s">
+      <c r="C56" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="D56" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E56" s="15"/>
-      <c r="F56" s="15"/>
+      <c r="D56" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E56" s="14"/>
+      <c r="F56" s="14"/>
     </row>
     <row r="57" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="11" t="s">
+      <c r="A57" s="10" t="s">
         <v>250</v>
       </c>
-      <c r="B57" s="11" t="s">
+      <c r="B57" s="10" t="s">
         <v>251</v>
       </c>
-      <c r="C57" s="13"/>
-      <c r="D57" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E57" s="15"/>
-      <c r="F57" s="15"/>
+      <c r="C57" s="12"/>
+      <c r="D57" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E57" s="14"/>
+      <c r="F57" s="14"/>
     </row>
     <row r="58" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="11" t="s">
+      <c r="A58" s="10" t="s">
         <v>252</v>
       </c>
-      <c r="B58" s="11" t="s">
+      <c r="B58" s="10" t="s">
         <v>253</v>
       </c>
-      <c r="C58" s="11" t="s">
+      <c r="C58" s="10" t="s">
         <v>254</v>
       </c>
-      <c r="D58" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E58" s="15"/>
-      <c r="F58" s="15"/>
+      <c r="D58" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E58" s="14"/>
+      <c r="F58" s="14"/>
     </row>
     <row r="59" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="11" t="s">
+      <c r="A59" s="10" t="s">
         <v>255</v>
       </c>
-      <c r="B59" s="11" t="s">
+      <c r="B59" s="10" t="s">
         <v>256</v>
       </c>
-      <c r="C59" s="11" t="s">
+      <c r="C59" s="10" t="s">
         <v>257</v>
       </c>
-      <c r="D59" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E59" s="15"/>
-      <c r="F59" s="15"/>
+      <c r="D59" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E59" s="14"/>
+      <c r="F59" s="14"/>
     </row>
     <row r="60" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="11" t="s">
+      <c r="A60" s="10" t="s">
         <v>258</v>
       </c>
-      <c r="B60" s="11" t="s">
+      <c r="B60" s="10" t="s">
         <v>259</v>
       </c>
-      <c r="C60" s="11" t="s">
+      <c r="C60" s="10" t="s">
         <v>260</v>
       </c>
-      <c r="D60" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E60" s="15"/>
-      <c r="F60" s="15"/>
+      <c r="D60" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E60" s="14"/>
+      <c r="F60" s="14"/>
     </row>
     <row r="61" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="11" t="s">
+      <c r="A61" s="10" t="s">
         <v>261</v>
       </c>
-      <c r="B61" s="11" t="s">
+      <c r="B61" s="10" t="s">
         <v>262</v>
       </c>
-      <c r="C61" s="11" t="s">
+      <c r="C61" s="10" t="s">
         <v>263</v>
       </c>
-      <c r="D61" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E61" s="15"/>
-      <c r="F61" s="15"/>
+      <c r="D61" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E61" s="14"/>
+      <c r="F61" s="14"/>
     </row>
     <row r="62" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="11" t="s">
+      <c r="A62" s="10" t="s">
         <v>264</v>
       </c>
-      <c r="B62" s="11" t="s">
+      <c r="B62" s="10" t="s">
         <v>265</v>
       </c>
-      <c r="C62" s="11" t="s">
+      <c r="C62" s="10" t="s">
         <v>266</v>
       </c>
-      <c r="D62" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E62" s="15"/>
-      <c r="F62" s="15"/>
+      <c r="D62" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E62" s="14"/>
+      <c r="F62" s="14"/>
     </row>
     <row r="63" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="11" t="s">
+      <c r="A63" s="10" t="s">
         <v>267</v>
       </c>
-      <c r="B63" s="11" t="s">
+      <c r="B63" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="C63" s="11" t="s">
+      <c r="C63" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="D63" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E63" s="15"/>
-      <c r="F63" s="15"/>
+      <c r="D63" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E63" s="14"/>
+      <c r="F63" s="14"/>
     </row>
     <row r="64" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="11" t="s">
+      <c r="A64" s="10" t="s">
         <v>269</v>
       </c>
-      <c r="B64" s="11" t="s">
+      <c r="B64" s="10" t="s">
         <v>270</v>
       </c>
-      <c r="C64" s="11" t="s">
+      <c r="C64" s="10" t="s">
         <v>271</v>
       </c>
-      <c r="D64" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E64" s="15"/>
-      <c r="F64" s="15"/>
+      <c r="D64" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E64" s="14"/>
+      <c r="F64" s="14"/>
     </row>
     <row r="65" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="11" t="s">
+      <c r="A65" s="10" t="s">
         <v>272</v>
       </c>
-      <c r="B65" s="11" t="s">
+      <c r="B65" s="10" t="s">
         <v>273</v>
       </c>
-      <c r="C65" s="11" t="s">
+      <c r="C65" s="10" t="s">
         <v>274</v>
       </c>
-      <c r="D65" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E65" s="15"/>
-      <c r="F65" s="15"/>
+      <c r="D65" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E65" s="14"/>
+      <c r="F65" s="14"/>
     </row>
     <row r="66" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="11" t="s">
+      <c r="A66" s="10" t="s">
         <v>275</v>
       </c>
-      <c r="B66" s="11" t="s">
+      <c r="B66" s="10" t="s">
         <v>276</v>
       </c>
-      <c r="C66" s="11" t="s">
+      <c r="C66" s="10" t="s">
         <v>277</v>
       </c>
-      <c r="D66" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E66" s="15"/>
-      <c r="F66" s="15"/>
+      <c r="D66" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E66" s="14"/>
+      <c r="F66" s="14"/>
     </row>
     <row r="67" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="11" t="s">
+      <c r="A67" s="10" t="s">
         <v>278</v>
       </c>
-      <c r="B67" s="11" t="s">
+      <c r="B67" s="10" t="s">
         <v>279</v>
       </c>
-      <c r="C67" s="11" t="s">
+      <c r="C67" s="10" t="s">
         <v>280</v>
       </c>
-      <c r="D67" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E67" s="15"/>
-      <c r="F67" s="15"/>
+      <c r="D67" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E67" s="14"/>
+      <c r="F67" s="14"/>
     </row>
     <row r="68" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="11" t="s">
+      <c r="A68" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="B68" s="11" t="s">
+      <c r="B68" s="10" t="s">
         <v>282</v>
       </c>
-      <c r="C68" s="11" t="s">
+      <c r="C68" s="10" t="s">
         <v>283</v>
       </c>
-      <c r="D68" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E68" s="15"/>
-      <c r="F68" s="15"/>
+      <c r="D68" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E68" s="14"/>
+      <c r="F68" s="14"/>
     </row>
     <row r="69" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="11" t="s">
+      <c r="A69" s="10" t="s">
         <v>284</v>
       </c>
-      <c r="B69" s="11" t="s">
+      <c r="B69" s="10" t="s">
         <v>285</v>
       </c>
-      <c r="C69" s="11" t="s">
+      <c r="C69" s="10" t="s">
         <v>286</v>
       </c>
-      <c r="D69" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E69" s="15"/>
-      <c r="F69" s="15"/>
+      <c r="D69" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E69" s="14"/>
+      <c r="F69" s="14"/>
     </row>
     <row r="70" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="11" t="s">
+      <c r="A70" s="10" t="s">
         <v>287</v>
       </c>
-      <c r="B70" s="11" t="s">
+      <c r="B70" s="10" t="s">
         <v>288</v>
       </c>
-      <c r="C70" s="11" t="s">
+      <c r="C70" s="10" t="s">
         <v>289</v>
       </c>
-      <c r="D70" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E70" s="15"/>
-      <c r="F70" s="15"/>
+      <c r="D70" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E70" s="14"/>
+      <c r="F70" s="14"/>
     </row>
     <row r="71" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="11" t="s">
+      <c r="A71" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="B71" s="11" t="s">
+      <c r="B71" s="10" t="s">
         <v>291</v>
       </c>
-      <c r="C71" s="11" t="s">
+      <c r="C71" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="D71" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E71" s="15"/>
-      <c r="F71" s="15"/>
+      <c r="D71" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E71" s="14"/>
+      <c r="F71" s="14"/>
     </row>
     <row r="72" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="11" t="s">
+      <c r="A72" s="10" t="s">
         <v>292</v>
       </c>
-      <c r="B72" s="11" t="s">
+      <c r="B72" s="10" t="s">
         <v>293</v>
       </c>
-      <c r="C72" s="11" t="s">
+      <c r="C72" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="D72" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E72" s="15"/>
-      <c r="F72" s="15"/>
+      <c r="D72" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E72" s="14"/>
+      <c r="F72" s="14"/>
     </row>
     <row r="73" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="11" t="s">
+      <c r="A73" s="10" t="s">
         <v>294</v>
       </c>
-      <c r="B73" s="11" t="s">
+      <c r="B73" s="10" t="s">
         <v>295</v>
       </c>
-      <c r="C73" s="11" t="s">
+      <c r="C73" s="10" t="s">
         <v>296</v>
       </c>
-      <c r="D73" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E73" s="15"/>
-      <c r="F73" s="15"/>
+      <c r="D73" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E73" s="14"/>
+      <c r="F73" s="14"/>
     </row>
     <row r="74" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A74" s="11" t="s">
+      <c r="A74" s="10" t="s">
         <v>297</v>
       </c>
-      <c r="B74" s="11" t="s">
+      <c r="B74" s="10" t="s">
         <v>295</v>
       </c>
-      <c r="C74" s="11" t="s">
+      <c r="C74" s="10" t="s">
         <v>298</v>
       </c>
-      <c r="D74" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E74" s="15"/>
-      <c r="F74" s="15"/>
+      <c r="D74" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E74" s="14"/>
+      <c r="F74" s="14"/>
     </row>
     <row r="75" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A75" s="11" t="s">
+      <c r="A75" s="10" t="s">
         <v>299</v>
       </c>
-      <c r="B75" s="11" t="s">
+      <c r="B75" s="10" t="s">
         <v>300</v>
       </c>
-      <c r="C75" s="11" t="s">
+      <c r="C75" s="10" t="s">
         <v>301</v>
       </c>
-      <c r="D75" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E75" s="15"/>
-      <c r="F75" s="15"/>
+      <c r="D75" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E75" s="14"/>
+      <c r="F75" s="14"/>
     </row>
     <row r="76" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="11" t="s">
+      <c r="A76" s="10" t="s">
         <v>302</v>
       </c>
-      <c r="B76" s="11" t="s">
+      <c r="B76" s="10" t="s">
         <v>303</v>
       </c>
-      <c r="C76" s="11" t="s">
+      <c r="C76" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="D76" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E76" s="15"/>
-      <c r="F76" s="15"/>
+      <c r="D76" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E76" s="14"/>
+      <c r="F76" s="14"/>
     </row>
     <row r="77" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="11" t="s">
+      <c r="A77" s="10" t="s">
         <v>304</v>
       </c>
-      <c r="B77" s="11" t="s">
+      <c r="B77" s="10" t="s">
         <v>305</v>
       </c>
-      <c r="C77" s="11" t="s">
+      <c r="C77" s="10" t="s">
         <v>306</v>
       </c>
-      <c r="D77" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E77" s="15"/>
-      <c r="F77" s="15"/>
+      <c r="D77" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E77" s="14"/>
+      <c r="F77" s="14"/>
     </row>
     <row r="78" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="11" t="s">
+      <c r="A78" s="10" t="s">
         <v>307</v>
       </c>
-      <c r="B78" s="11" t="s">
+      <c r="B78" s="10" t="s">
         <v>308</v>
       </c>
-      <c r="C78" s="11" t="s">
+      <c r="C78" s="10" t="s">
         <v>309</v>
       </c>
-      <c r="D78" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E78" s="15"/>
-      <c r="F78" s="15"/>
+      <c r="D78" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E78" s="14"/>
+      <c r="F78" s="14"/>
     </row>
     <row r="79" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="11" t="s">
+      <c r="A79" s="10" t="s">
         <v>310</v>
       </c>
-      <c r="B79" s="11" t="s">
+      <c r="B79" s="10" t="s">
         <v>311</v>
       </c>
-      <c r="C79" s="11" t="s">
+      <c r="C79" s="10" t="s">
         <v>312</v>
       </c>
-      <c r="D79" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E79" s="15"/>
-      <c r="F79" s="15"/>
+      <c r="D79" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E79" s="14"/>
+      <c r="F79" s="14"/>
     </row>
     <row r="80" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A80" s="11" t="s">
+      <c r="A80" s="10" t="s">
         <v>313</v>
       </c>
-      <c r="B80" s="11" t="s">
+      <c r="B80" s="10" t="s">
         <v>314</v>
       </c>
-      <c r="C80" s="11" t="s">
+      <c r="C80" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="D80" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E80" s="15"/>
-      <c r="F80" s="15"/>
+      <c r="D80" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E80" s="14"/>
+      <c r="F80" s="14"/>
     </row>
     <row r="81" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="11" t="s">
+      <c r="A81" s="10" t="s">
         <v>315</v>
       </c>
-      <c r="B81" s="11" t="s">
+      <c r="B81" s="10" t="s">
         <v>316</v>
       </c>
-      <c r="C81" s="11" t="s">
+      <c r="C81" s="10" t="s">
         <v>317</v>
       </c>
-      <c r="D81" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E81" s="15"/>
-      <c r="F81" s="15"/>
+      <c r="D81" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E81" s="14"/>
+      <c r="F81" s="14"/>
     </row>
     <row r="82" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="11" t="s">
+      <c r="A82" s="10" t="s">
         <v>318</v>
       </c>
-      <c r="B82" s="11" t="s">
+      <c r="B82" s="10" t="s">
         <v>319</v>
       </c>
-      <c r="C82" s="11" t="s">
+      <c r="C82" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="D82" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E82" s="15"/>
-      <c r="F82" s="15"/>
+      <c r="D82" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E82" s="14"/>
+      <c r="F82" s="14"/>
     </row>
     <row r="83" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A83" s="11" t="s">
+      <c r="A83" s="10" t="s">
         <v>321</v>
       </c>
-      <c r="B83" s="11" t="s">
+      <c r="B83" s="10" t="s">
         <v>322</v>
       </c>
-      <c r="C83" s="13"/>
-      <c r="D83" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E83" s="15"/>
-      <c r="F83" s="15"/>
+      <c r="C83" s="12"/>
+      <c r="D83" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E83" s="14"/>
+      <c r="F83" s="14"/>
     </row>
     <row r="84" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="11" t="s">
+      <c r="A84" s="10" t="s">
         <v>323</v>
       </c>
-      <c r="B84" s="11" t="s">
+      <c r="B84" s="10" t="s">
         <v>324</v>
       </c>
-      <c r="C84" s="11" t="s">
+      <c r="C84" s="10" t="s">
         <v>325</v>
       </c>
-      <c r="D84" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E84" s="15"/>
-      <c r="F84" s="15"/>
+      <c r="D84" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E84" s="14"/>
+      <c r="F84" s="14"/>
     </row>
     <row r="85" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="11" t="s">
+      <c r="A85" s="10" t="s">
         <v>326</v>
       </c>
-      <c r="B85" s="13"/>
-      <c r="C85" s="11" t="s">
+      <c r="B85" s="12"/>
+      <c r="C85" s="10" t="s">
         <v>327</v>
       </c>
-      <c r="D85" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E85" s="15"/>
-      <c r="F85" s="15"/>
+      <c r="D85" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E85" s="14"/>
+      <c r="F85" s="14"/>
     </row>
     <row r="86" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="11" t="s">
+      <c r="A86" s="10" t="s">
         <v>328</v>
       </c>
-      <c r="B86" s="11" t="s">
+      <c r="B86" s="10" t="s">
         <v>329</v>
       </c>
-      <c r="C86" s="11" t="s">
+      <c r="C86" s="10" t="s">
         <v>330</v>
       </c>
-      <c r="D86" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E86" s="15"/>
-      <c r="F86" s="15"/>
+      <c r="D86" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E86" s="14"/>
+      <c r="F86" s="14"/>
     </row>
     <row r="87" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="11" t="s">
+      <c r="A87" s="10" t="s">
         <v>331</v>
       </c>
-      <c r="B87" s="11" t="s">
+      <c r="B87" s="10" t="s">
         <v>329</v>
       </c>
-      <c r="C87" s="11" t="s">
+      <c r="C87" s="10" t="s">
         <v>332</v>
       </c>
-      <c r="D87" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E87" s="15"/>
-      <c r="F87" s="15"/>
+      <c r="D87" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E87" s="14"/>
+      <c r="F87" s="14"/>
     </row>
     <row r="88" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="11" t="s">
+      <c r="A88" s="10" t="s">
         <v>333</v>
       </c>
-      <c r="B88" s="11" t="s">
+      <c r="B88" s="10" t="s">
         <v>329</v>
       </c>
-      <c r="C88" s="11" t="s">
+      <c r="C88" s="10" t="s">
         <v>334</v>
       </c>
-      <c r="D88" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E88" s="15"/>
-      <c r="F88" s="15"/>
+      <c r="D88" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E88" s="14"/>
+      <c r="F88" s="14"/>
     </row>
     <row r="89" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="11" t="s">
+      <c r="A89" s="10" t="s">
         <v>335</v>
       </c>
-      <c r="B89" s="11" t="s">
+      <c r="B89" s="10" t="s">
         <v>329</v>
       </c>
-      <c r="C89" s="11" t="s">
+      <c r="C89" s="10" t="s">
         <v>336</v>
       </c>
-      <c r="D89" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E89" s="15"/>
-      <c r="F89" s="15"/>
+      <c r="D89" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E89" s="14"/>
+      <c r="F89" s="14"/>
     </row>
     <row r="90" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="11" t="s">
+      <c r="A90" s="10" t="s">
         <v>337</v>
       </c>
-      <c r="B90" s="11" t="s">
+      <c r="B90" s="10" t="s">
         <v>329</v>
       </c>
-      <c r="C90" s="11" t="s">
+      <c r="C90" s="10" t="s">
         <v>338</v>
       </c>
-      <c r="D90" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E90" s="15"/>
-      <c r="F90" s="15"/>
+      <c r="D90" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E90" s="14"/>
+      <c r="F90" s="14"/>
     </row>
     <row r="91" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A91" s="11" t="s">
+      <c r="A91" s="10" t="s">
         <v>339</v>
       </c>
-      <c r="B91" s="11" t="s">
+      <c r="B91" s="10" t="s">
         <v>329</v>
       </c>
-      <c r="C91" s="11" t="s">
+      <c r="C91" s="10" t="s">
         <v>340</v>
       </c>
-      <c r="D91" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E91" s="15"/>
-      <c r="F91" s="15"/>
+      <c r="D91" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E91" s="14"/>
+      <c r="F91" s="14"/>
     </row>
     <row r="92" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="11" t="s">
+      <c r="A92" s="10" t="s">
         <v>341</v>
       </c>
-      <c r="B92" s="11" t="s">
+      <c r="B92" s="10" t="s">
         <v>329</v>
       </c>
-      <c r="C92" s="11" t="s">
+      <c r="C92" s="10" t="s">
         <v>342</v>
       </c>
-      <c r="D92" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E92" s="15"/>
-      <c r="F92" s="15"/>
+      <c r="D92" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E92" s="14"/>
+      <c r="F92" s="14"/>
     </row>
     <row r="93" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="11" t="s">
+      <c r="A93" s="10" t="s">
         <v>343</v>
       </c>
-      <c r="B93" s="11" t="s">
+      <c r="B93" s="10" t="s">
         <v>329</v>
       </c>
-      <c r="C93" s="11" t="s">
+      <c r="C93" s="10" t="s">
         <v>344</v>
       </c>
-      <c r="D93" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E93" s="15"/>
-      <c r="F93" s="15"/>
+      <c r="D93" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E93" s="14"/>
+      <c r="F93" s="14"/>
     </row>
     <row r="94" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="11" t="s">
+      <c r="A94" s="10" t="s">
         <v>345</v>
       </c>
-      <c r="B94" s="11" t="s">
+      <c r="B94" s="10" t="s">
         <v>329</v>
       </c>
-      <c r="C94" s="11" t="s">
+      <c r="C94" s="10" t="s">
         <v>346</v>
       </c>
-      <c r="D94" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E94" s="15"/>
-      <c r="F94" s="15"/>
+      <c r="D94" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E94" s="14"/>
+      <c r="F94" s="14"/>
     </row>
     <row r="95" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="11" t="s">
+      <c r="A95" s="10" t="s">
         <v>347</v>
       </c>
-      <c r="B95" s="11" t="s">
+      <c r="B95" s="10" t="s">
         <v>329</v>
       </c>
-      <c r="C95" s="11" t="s">
+      <c r="C95" s="10" t="s">
         <v>348</v>
       </c>
-      <c r="D95" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E95" s="15"/>
-      <c r="F95" s="15"/>
+      <c r="D95" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E95" s="14"/>
+      <c r="F95" s="14"/>
     </row>
     <row r="96" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="11" t="s">
+      <c r="A96" s="10" t="s">
         <v>349</v>
       </c>
-      <c r="B96" s="11" t="s">
+      <c r="B96" s="10" t="s">
         <v>329</v>
       </c>
-      <c r="C96" s="11" t="s">
+      <c r="C96" s="10" t="s">
         <v>350</v>
       </c>
-      <c r="D96" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E96" s="15"/>
-      <c r="F96" s="15"/>
+      <c r="D96" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E96" s="14"/>
+      <c r="F96" s="14"/>
     </row>
     <row r="97" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A97" s="11" t="s">
+      <c r="A97" s="10" t="s">
         <v>351</v>
       </c>
-      <c r="B97" s="11" t="s">
+      <c r="B97" s="10" t="s">
         <v>329</v>
       </c>
-      <c r="C97" s="11" t="s">
+      <c r="C97" s="10" t="s">
         <v>352</v>
       </c>
-      <c r="D97" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E97" s="15"/>
-      <c r="F97" s="15"/>
+      <c r="D97" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E97" s="14"/>
+      <c r="F97" s="14"/>
     </row>
     <row r="98" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A98" s="11" t="s">
+      <c r="A98" s="10" t="s">
         <v>353</v>
       </c>
-      <c r="B98" s="11" t="s">
+      <c r="B98" s="10" t="s">
         <v>329</v>
       </c>
-      <c r="C98" s="11" t="s">
+      <c r="C98" s="10" t="s">
         <v>354</v>
       </c>
-      <c r="D98" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E98" s="15"/>
-      <c r="F98" s="15"/>
+      <c r="D98" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E98" s="14"/>
+      <c r="F98" s="14"/>
     </row>
     <row r="99" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A99" s="11" t="s">
+      <c r="A99" s="10" t="s">
         <v>355</v>
       </c>
-      <c r="B99" s="11" t="s">
+      <c r="B99" s="10" t="s">
         <v>329</v>
       </c>
-      <c r="C99" s="11" t="s">
+      <c r="C99" s="10" t="s">
         <v>356</v>
       </c>
-      <c r="D99" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E99" s="15"/>
-      <c r="F99" s="15"/>
+      <c r="D99" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E99" s="14"/>
+      <c r="F99" s="14"/>
     </row>
     <row r="100" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A100" s="11" t="s">
+      <c r="A100" s="10" t="s">
         <v>357</v>
       </c>
-      <c r="B100" s="11" t="s">
+      <c r="B100" s="10" t="s">
         <v>329</v>
       </c>
-      <c r="C100" s="11" t="s">
+      <c r="C100" s="10" t="s">
         <v>358</v>
       </c>
-      <c r="D100" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E100" s="15"/>
-      <c r="F100" s="15"/>
+      <c r="D100" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E100" s="14"/>
+      <c r="F100" s="14"/>
     </row>
     <row r="101" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A101" s="11" t="s">
+      <c r="A101" s="10" t="s">
         <v>359</v>
       </c>
-      <c r="B101" s="11" t="s">
+      <c r="B101" s="10" t="s">
         <v>360</v>
       </c>
-      <c r="C101" s="13"/>
-      <c r="D101" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E101" s="15"/>
-      <c r="F101" s="15"/>
+      <c r="C101" s="12"/>
+      <c r="D101" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E101" s="14"/>
+      <c r="F101" s="14"/>
     </row>
     <row r="102" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A102" s="11" t="s">
+      <c r="A102" s="10" t="s">
         <v>361</v>
       </c>
-      <c r="B102" s="11" t="s">
+      <c r="B102" s="10" t="s">
         <v>362</v>
       </c>
-      <c r="C102" s="11" t="s">
+      <c r="C102" s="10" t="s">
         <v>363</v>
       </c>
-      <c r="D102" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E102" s="15"/>
-      <c r="F102" s="15"/>
+      <c r="D102" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E102" s="14"/>
+      <c r="F102" s="14"/>
     </row>
     <row r="103" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A103" s="11" t="s">
+      <c r="A103" s="10" t="s">
         <v>364</v>
       </c>
-      <c r="B103" s="11" t="s">
+      <c r="B103" s="10" t="s">
         <v>365</v>
       </c>
-      <c r="C103" s="11" t="s">
+      <c r="C103" s="10" t="s">
         <v>366</v>
       </c>
-      <c r="D103" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E103" s="15"/>
-      <c r="F103" s="15"/>
+      <c r="D103" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E103" s="14"/>
+      <c r="F103" s="14"/>
     </row>
     <row r="104" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A104" s="11" t="s">
+      <c r="A104" s="10" t="s">
         <v>367</v>
       </c>
-      <c r="B104" s="11" t="s">
+      <c r="B104" s="10" t="s">
         <v>368</v>
       </c>
-      <c r="C104" s="11" t="s">
+      <c r="C104" s="10" t="s">
         <v>369</v>
       </c>
-      <c r="D104" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E104" s="15"/>
-      <c r="F104" s="15"/>
+      <c r="D104" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E104" s="14"/>
+      <c r="F104" s="14"/>
     </row>
     <row r="105" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A105" s="11" t="s">
+      <c r="A105" s="10" t="s">
         <v>370</v>
       </c>
-      <c r="B105" s="11" t="s">
+      <c r="B105" s="10" t="s">
         <v>365</v>
       </c>
-      <c r="C105" s="11" t="s">
+      <c r="C105" s="10" t="s">
         <v>371</v>
       </c>
-      <c r="D105" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E105" s="15"/>
-      <c r="F105" s="15"/>
+      <c r="D105" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E105" s="14"/>
+      <c r="F105" s="14"/>
     </row>
     <row r="106" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A106" s="11" t="s">
+      <c r="A106" s="10" t="s">
         <v>372</v>
       </c>
-      <c r="B106" s="11" t="s">
+      <c r="B106" s="10" t="s">
         <v>373</v>
       </c>
-      <c r="C106" s="11" t="s">
+      <c r="C106" s="10" t="s">
         <v>374</v>
       </c>
-      <c r="D106" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E106" s="15"/>
-      <c r="F106" s="15"/>
+      <c r="D106" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E106" s="14"/>
+      <c r="F106" s="14"/>
     </row>
     <row r="107" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A107" s="11" t="s">
+      <c r="A107" s="10" t="s">
         <v>375</v>
       </c>
-      <c r="B107" s="11" t="s">
+      <c r="B107" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C107" s="11" t="s">
+      <c r="C107" s="10" t="s">
         <v>376</v>
       </c>
-      <c r="D107" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E107" s="15"/>
-      <c r="F107" s="15"/>
+      <c r="D107" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E107" s="14"/>
+      <c r="F107" s="14"/>
     </row>
     <row r="108" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A108" s="11" t="s">
+      <c r="A108" s="10" t="s">
         <v>377</v>
       </c>
-      <c r="B108" s="11" t="s">
+      <c r="B108" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C108" s="11" t="s">
+      <c r="C108" s="10" t="s">
         <v>378</v>
       </c>
-      <c r="D108" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E108" s="15"/>
-      <c r="F108" s="15"/>
+      <c r="D108" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E108" s="14"/>
+      <c r="F108" s="14"/>
     </row>
     <row r="109" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A109" s="11" t="s">
+      <c r="A109" s="10" t="s">
         <v>379</v>
       </c>
-      <c r="B109" s="11" t="s">
+      <c r="B109" s="10" t="s">
         <v>380</v>
       </c>
-      <c r="C109" s="11" t="s">
+      <c r="C109" s="10" t="s">
         <v>381</v>
       </c>
-      <c r="D109" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E109" s="15"/>
-      <c r="F109" s="15"/>
+      <c r="D109" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E109" s="14"/>
+      <c r="F109" s="14"/>
     </row>
     <row r="110" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A110" s="11" t="s">
+      <c r="A110" s="10" t="s">
         <v>382</v>
       </c>
-      <c r="B110" s="11" t="s">
+      <c r="B110" s="10" t="s">
         <v>293</v>
       </c>
-      <c r="C110" s="11" t="s">
+      <c r="C110" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="D110" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E110" s="15"/>
-      <c r="F110" s="15"/>
+      <c r="D110" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E110" s="14"/>
+      <c r="F110" s="14"/>
     </row>
     <row r="111" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A111" s="11" t="s">
+      <c r="A111" s="10" t="s">
         <v>383</v>
       </c>
-      <c r="B111" s="11" t="s">
+      <c r="B111" s="10" t="s">
         <v>384</v>
       </c>
-      <c r="C111" s="11" t="s">
+      <c r="C111" s="10" t="s">
         <v>385</v>
       </c>
-      <c r="D111" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E111" s="15"/>
-      <c r="F111" s="15"/>
+      <c r="D111" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E111" s="14"/>
+      <c r="F111" s="14"/>
     </row>
     <row r="112" spans="1:6" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A112" s="11" t="s">
+      <c r="A112" s="10" t="s">
         <v>386</v>
       </c>
-      <c r="B112" s="11" t="s">
+      <c r="B112" s="10" t="s">
         <v>387</v>
       </c>
-      <c r="C112" s="11" t="s">
+      <c r="C112" s="10" t="s">
         <v>289</v>
       </c>
-      <c r="D112" s="12">
-        <v>2025</v>
-      </c>
-      <c r="E112" s="15"/>
-      <c r="F112" s="15"/>
+      <c r="D112" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E112" s="14"/>
+      <c r="F112" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
